--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506103524119764</v>
+        <v>0.6506095211420664</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514139037657211</v>
+        <v>0.6514134653390329</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524748804080081</v>
+        <v>0.6524741308534012</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497293050916397</v>
+        <v>0.6497289895440699</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464290083190002</v>
+        <v>0.6464286687938708</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643138694117697</v>
+        <v>0.643138319928278</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640821655179068</v>
+        <v>0.6408212588763529</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398062738842233</v>
+        <v>0.6398058770317845</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423863261548197</v>
+        <v>0.6423844582254055</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432641161926806</v>
+        <v>0.6432629997619637</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413570725856377</v>
+        <v>0.6413559632559553</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384801014341998</v>
+        <v>0.6384789779452829</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403587645400471</v>
+        <v>0.6403554608838635</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640434071267278</v>
+        <v>0.6404308800555346</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399172349179736</v>
+        <v>0.6399155838725981</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.642289778378787</v>
+        <v>0.6422884437611769</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.645039473597395</v>
+        <v>0.6450368958369292</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469376163626611</v>
+        <v>0.6469342106632125</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465775163254985</v>
+        <v>0.6465746339150601</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646792522729752</v>
+        <v>0.6467908616275871</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455809298815123</v>
+        <v>0.6455781361954919</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450530595644463</v>
+        <v>0.6450482116016519</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458734392088086</v>
+        <v>0.6458651281224357</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6436601196701378</v>
+        <v>0.6436492581269632</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6428271294461293</v>
+        <v>0.642813306574191</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6439816043439076</v>
+        <v>0.6439657266998065</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.644566643338082</v>
+        <v>0.6445498430646044</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6463730645469965</v>
+        <v>0.6463534859842948</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6530701487122259</v>
+        <v>0.6530537062767607</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6650119831601375</v>
+        <v>0.6649886734514443</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.672301556543502</v>
+        <v>0.6722754531588826</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6881917148784533</v>
+        <v>0.6881680253157233</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6973009997219253</v>
+        <v>0.6972831612873804</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.699670974409989</v>
+        <v>0.6996522941430701</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6999490120254721</v>
+        <v>0.699929979902018</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080477169649309</v>
+        <v>0.708042197302845</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080765407065852</v>
+        <v>0.7080722756540716</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108903278266847</v>
+        <v>0.7108931054027344</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7172803873532654</v>
+        <v>0.7172974527344306</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7174609067693982</v>
+        <v>0.7174790489154743</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7245492643848499</v>
+        <v>0.7245743417372916</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.719898953007983</v>
+        <v>0.719909598208436</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7232610368688908</v>
+        <v>0.7232731955965824</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7227769869658368</v>
+        <v>0.7227873779725457</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199352658805388</v>
+        <v>0.719943667092411</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714738328474565</v>
+        <v>0.7147384294141079</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166249047042641</v>
+        <v>0.7166263689636995</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166096146812162</v>
+        <v>0.7166131930150668</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153173779048605</v>
+        <v>0.7153213289133172</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130685363009241</v>
+        <v>0.7130711763356792</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106144552431708</v>
+        <v>0.7106184631521085</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106347039888451</v>
+        <v>0.710639204767018</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084468313725846</v>
+        <v>0.7084538111323126</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7058783351266746</v>
+        <v>0.7058914152669542</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040097703079026</v>
+        <v>0.7040246036721912</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7031554417078003</v>
+        <v>0.7031685590715522</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026550865787853</v>
+        <v>0.7026641578478919</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032120193957671</v>
+        <v>0.703213620191027</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050253794398791</v>
+        <v>0.7050171885757922</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.706767496285273</v>
+        <v>0.7067445679515871</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7087811321582813</v>
+        <v>0.7090955335978255</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7090397803537001</v>
+        <v>0.7093638960695972</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7085477190716527</v>
+        <v>0.7089406509748644</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7083263925573228</v>
+        <v>0.7087633526530435</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7079889264664335</v>
+        <v>0.7084868033502405</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.708816646416504</v>
+        <v>0.7093508168268972</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7109262838285452</v>
+        <v>0.7114736640557853</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7158494533278632</v>
+        <v>0.7163614504503309</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7207588207418882</v>
+        <v>0.7212006974156124</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7250768936098204</v>
+        <v>0.7254257021109443</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7284488138686254</v>
+        <v>0.7286311248627342</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7331566652888624</v>
+        <v>0.7329701440866545</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7421931069736389</v>
+        <v>0.7410623281584724</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7306965014495234</v>
+        <v>0.7304412346312313</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B115"/>
+  <dimension ref="A1:B116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506095211420664</v>
+        <v>0.6506087073706157</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514134653390329</v>
+        <v>0.6514130360212739</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524741308534012</v>
+        <v>0.6524733969966896</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497289895440699</v>
+        <v>0.6497286803986091</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464286687938708</v>
+        <v>0.646428336185592</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643138319928278</v>
+        <v>0.6431379533895308</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408212588763529</v>
+        <v>0.640820870693795</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398058770317845</v>
+        <v>0.6398054883201881</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423844582254055</v>
+        <v>0.6423826298088948</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432629997619637</v>
+        <v>0.6432619071415968</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413559632559553</v>
+        <v>0.6413548775685944</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384789779452829</v>
+        <v>0.63847787838702</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403554608838635</v>
+        <v>0.6403522274310272</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404308800555346</v>
+        <v>0.6404277561622065</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399155838725981</v>
+        <v>0.6399139673438441</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422884437611769</v>
+        <v>0.6422871378406034</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450368958369292</v>
+        <v>0.6450343729262173</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469342106632125</v>
+        <v>0.6469308763071886</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465746339150601</v>
+        <v>0.6465718114772917</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467908616275871</v>
+        <v>0.646789235238397</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455781361954919</v>
+        <v>0.6455754010990468</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450482116016519</v>
+        <v>0.6450434660695681</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458651281224357</v>
+        <v>0.6458569912686589</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6436492581269632</v>
+        <v>0.6436386238619751</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.642813306574191</v>
+        <v>0.6427997729559518</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6439657266998065</v>
+        <v>0.643950180311921</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6445498430646044</v>
+        <v>0.6445333922518244</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6463534859842948</v>
+        <v>0.6463343150993084</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6530537062767607</v>
+        <v>0.6530376100808777</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6649886734514443</v>
+        <v>0.6649658518156629</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6722754531588826</v>
+        <v>0.6722498968220703</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6881680253157233</v>
+        <v>0.6881448236817178</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6972831612873804</v>
+        <v>0.6972656890256881</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6996522941430701</v>
+        <v>0.6996339945317134</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.699929979902018</v>
+        <v>0.6999113309174543</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.708042197302845</v>
+        <v>0.7080367810381231</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080722756540716</v>
+        <v>0.7080680863356077</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108931054027344</v>
+        <v>0.7108958114839092</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7172974527344306</v>
+        <v>0.7173141599362719</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7174790489154743</v>
+        <v>0.7174968136085487</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7245743417372916</v>
+        <v>0.7245989044099124</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.719909598208436</v>
+        <v>0.7199200238216719</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7232731955965824</v>
+        <v>0.7232851047610188</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7227873779725457</v>
+        <v>0.7227975594026532</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.719943667092411</v>
+        <v>0.7199519017127293</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147384294141079</v>
+        <v>0.7147385294420421</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166263689636995</v>
+        <v>0.7166278064834296</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166131930150668</v>
+        <v>0.7166166994005807</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153213289133172</v>
+        <v>0.7153251982783018</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130711763356792</v>
+        <v>0.7130737579419235</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106184631521085</v>
+        <v>0.7106223792991297</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.710639204767018</v>
+        <v>0.7106436027252891</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084538111323126</v>
+        <v>0.7084606349710297</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7058914152669542</v>
+        <v>0.705904223726701</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040246036721912</v>
+        <v>0.7040391424394277</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7031685590715522</v>
+        <v>0.7031814285620823</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026641578478919</v>
+        <v>0.7026730802976114</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.703213620191027</v>
+        <v>0.7032152360206088</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050171885757922</v>
+        <v>0.7050092192319055</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7067445679515871</v>
+        <v>0.7067221391222278</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7090955335978255</v>
+        <v>0.7090620297133992</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7093638960695972</v>
+        <v>0.7096883488763767</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7089406509748644</v>
+        <v>0.7093260256820528</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7087633526530435</v>
+        <v>0.7091353307740198</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7084868033502405</v>
+        <v>0.7089592854017455</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7093508168268972</v>
+        <v>0.7098201723242737</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7114736640557853</v>
+        <v>0.7119491104084817</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7163614504503309</v>
+        <v>0.7168010568831094</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7212006974156124</v>
+        <v>0.7215815040043834</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7254257021109443</v>
+        <v>0.7257049338530753</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7286311248627342</v>
+        <v>0.7287951585998254</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7329701440866545</v>
+        <v>0.7328073306312807</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7410623281584724</v>
+        <v>0.7400995359220433</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,15 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7304412346312313</v>
+        <v>0.7302024073358957</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>0.7284836173086973</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506087073706157</v>
+        <v>0.6506079105508777</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514130360212739</v>
+        <v>0.6514126155315551</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524733969966896</v>
+        <v>0.6524726783498883</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497286803986091</v>
+        <v>0.649728377462664</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.646428336185592</v>
+        <v>0.6464280102851809</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431379533895308</v>
+        <v>0.6431375942694195</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640820870693795</v>
+        <v>0.640820490384569</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398054883201881</v>
+        <v>0.6398051075016844</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423826298088948</v>
+        <v>0.6423808396648995</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432619071415968</v>
+        <v>0.6432608375781466</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413548775685944</v>
+        <v>0.6413538147759458</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.63847787838702</v>
+        <v>0.6384768020030951</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403522274310272</v>
+        <v>0.640349061968069</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404277561622065</v>
+        <v>0.6404246974804005</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399139673438441</v>
+        <v>0.6399123842608024</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422871378406034</v>
+        <v>0.6422858597019121</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450343729262173</v>
+        <v>0.6450319031340763</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469308763071886</v>
+        <v>0.6469276110778113</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465718114772917</v>
+        <v>0.6465690471610812</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646789235238397</v>
+        <v>0.6467876424861041</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455754010990468</v>
+        <v>0.6455727227694983</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450434660695681</v>
+        <v>0.6450388197580745</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458569912686589</v>
+        <v>0.6458490232283998</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6436386238619751</v>
+        <v>0.6436282098211445</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6427997729559518</v>
+        <v>0.642786519615145</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.643950180311921</v>
+        <v>0.6439349549335462</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6445333922518244</v>
+        <v>0.6445172801246282</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6463343150993084</v>
+        <v>0.6463155393112529</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6530376100808777</v>
+        <v>0.6530218493164615</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6649658518156629</v>
+        <v>0.664943503106193</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6722498968220703</v>
+        <v>0.672224870541933</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6881448236817178</v>
+        <v>0.6881220950836469</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6972656890256881</v>
+        <v>0.6972485718013779</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6996339945317134</v>
+        <v>0.6996160640903715</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6999113309174543</v>
+        <v>0.6998930536630009</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080367810381231</v>
+        <v>0.7080314653358845</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080680863356077</v>
+        <v>0.7080639708156075</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7108958114839092</v>
+        <v>0.710898448693571</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7173141599362719</v>
+        <v>0.7173305201003535</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7174968136085487</v>
+        <v>0.7175142124824992</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7245989044099124</v>
+        <v>0.7246229680606537</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7199200238216719</v>
+        <v>0.7199302365582316</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7232851047610188</v>
+        <v>0.7232967719475039</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7227975594026532</v>
+        <v>0.722807537510048</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199519017127293</v>
+        <v>0.7199599746250195</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147385294420421</v>
+        <v>0.7147386285498333</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166278064834296</v>
+        <v>0.7166292179747427</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166166994005807</v>
+        <v>0.7166201359826632</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153251982783018</v>
+        <v>0.7153289885058935</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130737579419235</v>
+        <v>0.7130762830351689</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106223792991297</v>
+        <v>0.7106262067762101</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106436027252891</v>
+        <v>0.7106479013208475</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084606349710297</v>
+        <v>0.7084673080221287</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.705904223726701</v>
+        <v>0.7059167688383163</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040391424394277</v>
+        <v>0.7040533952174803</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7031814285620823</v>
+        <v>0.7031940570123898</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026730802976114</v>
+        <v>0.7026818572920078</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032152360206088</v>
+        <v>0.7032168650343263</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050092192319055</v>
+        <v>0.7050014632475705</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7067221391222278</v>
+        <v>0.7067001941196027</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7090620297133992</v>
+        <v>0.7090291914036142</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7096883488763767</v>
+        <v>0.7100229422874044</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7093260256820528</v>
+        <v>0.7097236160907681</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7091353307740198</v>
+        <v>0.70952505469455</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7089592854017455</v>
+        <v>0.7094660380073359</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7098201723242737</v>
+        <v>0.7103064961315095</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7119491104084817</v>
+        <v>0.7124444862667463</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7168010568831094</v>
+        <v>0.7172658590997323</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7215815040043834</v>
+        <v>0.7219941921124617</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7257049338530753</v>
+        <v>0.7260246631358345</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7287951585998254</v>
+        <v>0.7290119767226111</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7328073306312807</v>
+        <v>0.7327364232745497</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7400995359220433</v>
+        <v>0.739360276632689</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7302024073358957</v>
+        <v>0.7301493134995161</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7284836173086973</v>
+        <v>0.7289898501663631</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506079105508777</v>
+        <v>0.6506071301586485</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514126155315551</v>
+        <v>0.651412203600416</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524726783498883</v>
+        <v>0.6524719744450287</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649728377462664</v>
+        <v>0.649728080551278</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464280102851809</v>
+        <v>0.646427690891979</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431375942694195</v>
+        <v>0.643137242345188</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640820490384569</v>
+        <v>0.6408201177117439</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398051075016844</v>
+        <v>0.6398047343384673</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423808396648995</v>
+        <v>0.642379086604402</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432608375781466</v>
+        <v>0.6432597903496259</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413538147759458</v>
+        <v>0.6413527741615838</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384768020030951</v>
+        <v>0.6384757480687226</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640349061968069</v>
+        <v>0.6403459623735743</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404246974804005</v>
+        <v>0.640421701990197</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399123842608024</v>
+        <v>0.639910833596399</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422858597019121</v>
+        <v>0.6422846084684288</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450319031340763</v>
+        <v>0.6450294848013766</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469276110778113</v>
+        <v>0.6469244128491286</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465690471610812</v>
+        <v>0.6465663391906677</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467876424861041</v>
+        <v>0.6467860823386198</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455727227694983</v>
+        <v>0.6455700994589408</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450388197580745</v>
+        <v>0.6450342695897122</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458490232283998</v>
+        <v>0.6458412188048831</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6436282098211445</v>
+        <v>0.6436180092391318</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.642786519615145</v>
+        <v>0.6427735379427446</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6439349549335462</v>
+        <v>0.6439200407357584</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6445172801246282</v>
+        <v>0.6445014963457141</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6463155393112529</v>
+        <v>0.6462971465508547</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6530218493164615</v>
+        <v>0.6530064136200273</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.664943503106193</v>
+        <v>0.6649216127957853</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.672224870541933</v>
+        <v>0.6722003580226801</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6881220950836469</v>
+        <v>0.6880998252275509</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6972485718013779</v>
+        <v>0.6972317989249458</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6996160640903715</v>
+        <v>0.6995984917896381</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6998930536630009</v>
+        <v>0.6998751371764911</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080314653358845</v>
+        <v>0.7080262474620003</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080639708156075</v>
+        <v>0.7080599272208949</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.710898448693571</v>
+        <v>0.7109010195315958</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7173305201003535</v>
+        <v>0.7173465439116053</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7175142124824992</v>
+        <v>0.7175312566989475</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7246229680606537</v>
+        <v>0.7246465477197452</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7199302365582316</v>
+        <v>0.7199402428585779</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7232967719475039</v>
+        <v>0.7233082044378578</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.722807537510048</v>
+        <v>0.7228173183032145</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199599746250195</v>
+        <v>0.7199678905247384</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147386285498333</v>
+        <v>0.7147387267307823</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166292179747427</v>
+        <v>0.716630604124574</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166201359826632</v>
+        <v>0.7166235048219326</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153289885058935</v>
+        <v>0.7153327020005855</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130762830351689</v>
+        <v>0.7130787534482333</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106262067762101</v>
+        <v>0.7106299485388522</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106479013208475</v>
+        <v>0.7106521038586014</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084673080221287</v>
+        <v>0.7084738351973789</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7059167688383163</v>
+        <v>0.7059290585987372</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040533952174803</v>
+        <v>0.7040673702855216</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7031940570123898</v>
+        <v>0.7032064510121256</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026818572920078</v>
+        <v>0.7026904921075769</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032168650343263</v>
+        <v>0.7032185055087483</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7050014632475705</v>
+        <v>0.7049939128373611</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7067001941196027</v>
+        <v>0.7066787178979963</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7090291914036142</v>
+        <v>0.7089969996340288</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7100229422874044</v>
+        <v>0.7102377358031835</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7097236160907681</v>
+        <v>0.7099806925513226</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.70952505469455</v>
+        <v>0.7097582520024048</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7094660380073359</v>
+        <v>0.7097474811025922</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7103064961315095</v>
+        <v>0.7105918914252651</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7124444862667463</v>
+        <v>0.7127174948909172</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7172658590997323</v>
+        <v>0.7174759750078201</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7219941921124617</v>
+        <v>0.7221120937188521</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7260246631358345</v>
+        <v>0.7260107606699058</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7290119767226111</v>
+        <v>0.7288060597413439</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7327364232745497</v>
+        <v>0.7321423069040283</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.739360276632689</v>
+        <v>0.7379803337747425</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7301493134995161</v>
+        <v>0.7289355614649269</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7289898501663631</v>
+        <v>0.7253253120023286</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506071301586485</v>
+        <v>0.6506063656911159</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.651412203600416</v>
+        <v>0.6514117999692495</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524719744450287</v>
+        <v>0.6524712848331433</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649728080551278</v>
+        <v>0.6497277894867564</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.646427690891979</v>
+        <v>0.6464273778132422</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643137242345188</v>
+        <v>0.643136897402901</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408201177117439</v>
+        <v>0.6408197524477925</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398047343384673</v>
+        <v>0.6398043686021808</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642379086604402</v>
+        <v>0.6423773694871235</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432597903496259</v>
+        <v>0.6432587647638708</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413527741615838</v>
+        <v>0.6413517550386563</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384757480687226</v>
+        <v>0.6384747158890193</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403459623735743</v>
+        <v>0.6403429266134482</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640421701990197</v>
+        <v>0.6404187677542088</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639910833596399</v>
+        <v>0.6399093143651764</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422846084684288</v>
+        <v>0.6422833832999599</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450294848013766</v>
+        <v>0.6450271163373336</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469244128491286</v>
+        <v>0.6469212795814143</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465663391906677</v>
+        <v>0.6465636858618485</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467860823386198</v>
+        <v>0.6467845538056219</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455700994589408</v>
+        <v>0.6455675294904508</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450342695897122</v>
+        <v>0.6450298126129028</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458412188048831</v>
+        <v>0.6458335730123597</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6436180092391318</v>
+        <v>0.64360801562468</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6427735379427446</v>
+        <v>0.6427608196783939</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6439200407357584</v>
+        <v>0.643905428286363</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6445014963457141</v>
+        <v>0.6444860309936123</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6462971465508547</v>
+        <v>0.6462791252346618</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6530064136200273</v>
+        <v>0.6529912930501187</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6649216127957853</v>
+        <v>0.6649001669452541</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6722003580226801</v>
+        <v>0.672176343628706</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6880998252275509</v>
+        <v>0.6880780003885602</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6972317989249458</v>
+        <v>0.6972153601308013</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6995984917896381</v>
+        <v>0.6995812670338935</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6998751371764911</v>
+        <v>0.699857570920827</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080262474620003</v>
+        <v>0.7080211247787673</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080599272208949</v>
+        <v>0.7080559537383881</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109010195315958</v>
+        <v>0.7109035263814159</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7173465439116053</v>
+        <v>0.717362241621444</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7175312566989475</v>
+        <v>0.7175479569709301</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7246465477197452</v>
+        <v>0.7246696578207951</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7199402428585779</v>
+        <v>0.7199500489065171</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7233082044378578</v>
+        <v>0.7233194092254016</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228173183032145</v>
+        <v>0.7228269075571025</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199678905247384</v>
+        <v>0.7199756539281914</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147387267307823</v>
+        <v>0.7147388239798597</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.716630604124574</v>
+        <v>0.7166319655965023</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166235048219326</v>
+        <v>0.7166268078988132</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153327020005855</v>
+        <v>0.7153363410703828</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130787534482333</v>
+        <v>0.7130811709356488</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106299485388522</v>
+        <v>0.7106336074134898</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106521038586014</v>
+        <v>0.7106562134994256</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084738351973789</v>
+        <v>0.7084802211986987</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7059290585987372</v>
+        <v>0.7059411006860589</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040673702855216</v>
+        <v>0.7040810756093914</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7032064510121256</v>
+        <v>0.7032186169180292</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026904921075769</v>
+        <v>0.7026989879352306</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032185055087483</v>
+        <v>0.7032201558385082</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049939128373611</v>
+        <v>0.7049865605705814</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7066787178979963</v>
+        <v>0.7066576960128791</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7089969996340288</v>
+        <v>0.7089654360652522</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7102377358031835</v>
+        <v>0.7104099775479591</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7099806925513226</v>
+        <v>0.710186345815826</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7097582520024048</v>
+        <v>0.7099391760061314</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7097474811025922</v>
+        <v>0.7099476207123996</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7105918914252651</v>
+        <v>0.7108009880782826</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7127174948909172</v>
+        <v>0.7129041335229258</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7174759750078201</v>
+        <v>0.7175852314279021</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7221120937188521</v>
+        <v>0.7221116618893448</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7260107606699058</v>
+        <v>0.7258625670987502</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7288060597413439</v>
+        <v>0.7284261463646609</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7321423069040283</v>
+        <v>0.7313503450099785</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7379803337747425</v>
+        <v>0.7364099024525643</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7289355614649269</v>
+        <v>0.7273725021312771</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7253253120023286</v>
+        <v>0.7218940501148966</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506063656911159</v>
+        <v>0.6506056166657799</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514117999692495</v>
+        <v>0.6514114043897608</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524712848331433</v>
+        <v>0.6524706090833112</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497277894867564</v>
+        <v>0.6497275040983145</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464273778132422</v>
+        <v>0.6464270708637557</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643136897402901</v>
+        <v>0.6431365592370129</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408197524477925</v>
+        <v>0.6408193943741307</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398043686021808</v>
+        <v>0.6398040100734549</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423773694871235</v>
+        <v>0.6423756872190528</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432587647638708</v>
+        <v>0.6432577601570174</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413517550386563</v>
+        <v>0.6413507567483762</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384747158890193</v>
+        <v>0.6384737047974808</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403429266134482</v>
+        <v>0.640339952736469</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404187677542088</v>
+        <v>0.6404158929134099</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399093143651764</v>
+        <v>0.639907825621207</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422833832999599</v>
+        <v>0.642282183390915</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450271163373336</v>
+        <v>0.6450247962160279</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469212795814143</v>
+        <v>0.6469182093168435</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465636858618485</v>
+        <v>0.6465610855384138</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467845538056219</v>
+        <v>0.6467830559364647</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455675294904508</v>
+        <v>0.6455650112545211</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450298126129028</v>
+        <v>0.6450254459955835</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458335730123597</v>
+        <v>0.6458260810655079</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.64360801562468</v>
+        <v>0.6435982227468841</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6427608196783939</v>
+        <v>0.6427483568929466</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.643905428286363</v>
+        <v>0.6438911085301025</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6444860309936123</v>
+        <v>0.6444708745420155</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6462791252346618</v>
+        <v>0.6462614642408819</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6529912930501187</v>
+        <v>0.6529764780660672</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6649001669452541</v>
+        <v>0.6648791521740627</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.672176343628706</v>
+        <v>0.6721528123515454</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6880780003885602</v>
+        <v>0.6880566073829066</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6972153601308013</v>
+        <v>0.6971992455565066</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6995812670338935</v>
+        <v>0.6995643796402493</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.699857570920827</v>
+        <v>0.6998403447636655</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080211247787673</v>
+        <v>0.7080160947407917</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080559537383881</v>
+        <v>0.7080520486128712</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109035263814159</v>
+        <v>0.7109059715165935</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.717362241621444</v>
+        <v>0.7173776230695044</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7175479569709301</v>
+        <v>0.7175643235851662</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7246696578207951</v>
+        <v>0.724692312230053</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7199500489065171</v>
+        <v>0.7199596606418293</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7233194092254016</v>
+        <v>0.7233303930290655</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228269075571025</v>
+        <v>0.7228363108243177</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199756539281914</v>
+        <v>0.7199832691809487</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147388239798597</v>
+        <v>0.7147389202935516</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166319655965023</v>
+        <v>0.7166333030316998</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166268078988132</v>
+        <v>0.7166300471173931</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153363410703828</v>
+        <v>0.715339907931596</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130811709356488</v>
+        <v>0.7130835371777897</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106336074134898</v>
+        <v>0.7106371861044185</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106562134994256</v>
+        <v>0.7106602332678795</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084802211986987</v>
+        <v>0.7084864705291881</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7059411006860589</v>
+        <v>0.7059529024751833</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040810756093914</v>
+        <v>0.7040945188561174</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7032186169180292</v>
+        <v>0.7032305608638527</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7026989879352306</v>
+        <v>0.7027073478822998</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032201558385082</v>
+        <v>0.7032218145282543</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049865605705814</v>
+        <v>0.7049793993520568</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7066576960128791</v>
+        <v>0.7066371145919391</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7089654360652522</v>
+        <v>0.7089344830227126</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7104099775479591</v>
+        <v>0.7105752219231636</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.710186345815826</v>
+        <v>0.710378892618926</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7099391760061314</v>
+        <v>0.7101097072275223</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7099476207123996</v>
+        <v>0.710146387171937</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7108009880782826</v>
+        <v>0.7110268362666441</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7129041335229258</v>
+        <v>0.7131405560942768</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7175852314279021</v>
+        <v>0.71778808444519</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7221116618893448</v>
+        <v>0.7222682063533877</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7258625670987502</v>
+        <v>0.7259489629299741</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7284261463646609</v>
+        <v>0.7284556854351334</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7313503450099785</v>
+        <v>0.7311579119912177</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7364099024525643</v>
+        <v>0.7357418488440037</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7273725021312771</v>
+        <v>0.7271236598651082</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7218940501148966</v>
+        <v>0.7221917432369029</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506056166657799</v>
+        <v>0.6506048826194374</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514114043897608</v>
+        <v>0.651411016623459</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524706090833112</v>
+        <v>0.6524699467817601</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497275040983145</v>
+        <v>0.6497272242217446</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464270708637557</v>
+        <v>0.6464267698654688</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431365592370129</v>
+        <v>0.6431362276499594</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408193943741307</v>
+        <v>0.6408190432806811</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398040100734549</v>
+        <v>0.6398036585414677</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423756872190528</v>
+        <v>0.6423740387501233</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432577601570174</v>
+        <v>0.6432567758920695</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413507567483762</v>
+        <v>0.6413497786586015</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384737047974808</v>
+        <v>0.6384727141545467</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640339952736469</v>
+        <v>0.6403370388701133</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404158929134099</v>
+        <v>0.6404130756832165</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639907825621207</v>
+        <v>0.639906366456132</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.642282183390915</v>
+        <v>0.6422810079685446</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450247962160279</v>
+        <v>0.6450225229731323</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469182093168435</v>
+        <v>0.646915200175425</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465610855384138</v>
+        <v>0.6465585366487903</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467830559364647</v>
+        <v>0.646781587818212</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455650112545211</v>
+        <v>0.6455625432057093</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450254459955835</v>
+        <v>0.6450211670192215</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458260810655079</v>
+        <v>0.6458187383694669</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435982227468841</v>
+        <v>0.6435886246222791</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6427483568929466</v>
+        <v>0.6427361419720474</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6438911085301025</v>
+        <v>0.6438770727700349</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6444708745420155</v>
+        <v>0.6444560178403261</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6462614642408819</v>
+        <v>0.646244152886647</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6529764780660672</v>
+        <v>0.6529619595080214</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6648791521740627</v>
+        <v>0.6648585556326562</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6721528123515454</v>
+        <v>0.6721297497787881</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6880566073829066</v>
+        <v>0.6880356335415666</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6971992455565066</v>
+        <v>0.6971834457232227</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6995643796402493</v>
+        <v>0.6995478198187035</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6998403447636655</v>
+        <v>0.69982344895825</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080160947407917</v>
+        <v>0.7080111548910795</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080520486128712</v>
+        <v>0.708048210144854</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109059715165935</v>
+        <v>0.7109083571069611</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7173776230695044</v>
+        <v>0.7173926977040803</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7175643235851662</v>
+        <v>0.7175803664230112</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.724692312230053</v>
+        <v>0.7247145242739723</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7199596606418293</v>
+        <v>0.719969083772163</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7233303930290655</v>
+        <v>0.7233411623066804</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228363108243177</v>
+        <v>0.7228455334456783</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199832691809487</v>
+        <v>0.7199907404657977</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147389202935516</v>
+        <v>0.714739015669722</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166333030316998</v>
+        <v>0.7166346170498397</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166300471173931</v>
+        <v>0.7166332243090622</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.715339907931596</v>
+        <v>0.7153434047133549</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130835371777897</v>
+        <v>0.7130858537847449</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106371861044185</v>
+        <v>0.7106406872002868</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106602332678795</v>
+        <v>0.7106641660594385</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084864705291881</v>
+        <v>0.7084925875034762</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7059529024751833</v>
+        <v>0.7059644710525604</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7040945188561174</v>
+        <v>0.7041077074076457</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7032305608638527</v>
+        <v>0.7032422887697998</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027073478822998</v>
+        <v>0.7027155749745505</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032218145282543</v>
+        <v>0.7032234801851862</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049793993520568</v>
+        <v>0.7049724224041251</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7066371145919391</v>
+        <v>0.7066169603077302</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7089344830227126</v>
+        <v>0.7089041234679162</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7105752219231636</v>
+        <v>0.7107033733537093</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.710378892618926</v>
+        <v>0.7105277472563598</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7101097072275223</v>
+        <v>0.7102372774678867</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.710146387171937</v>
+        <v>0.7102961701583077</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7110268362666441</v>
+        <v>0.7112002419438171</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7131405560942768</v>
+        <v>0.7133214376898012</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.71778808444519</v>
+        <v>0.7179317808341756</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7222682063533877</v>
+        <v>0.7223623720569323</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7259489629299741</v>
+        <v>0.7259735997548482</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7284556854351334</v>
+        <v>0.7284252553718917</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7311579119912177</v>
+        <v>0.7309210715700816</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7357418488440037</v>
+        <v>0.7350819523979273</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7271236598651082</v>
+        <v>0.7268407358130384</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7221917432369029</v>
+        <v>0.7222730597555926</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B116"/>
+  <dimension ref="A1:B117"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506048826194374</v>
+        <v>0.6506041631072268</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.651411016623459</v>
+        <v>0.6514106364411777</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524699467817601</v>
+        <v>0.6524692975310211</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497272242217446</v>
+        <v>0.6497269496991041</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464267698654688</v>
+        <v>0.6464264746471535</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431362276499594</v>
+        <v>0.6431359024517755</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408190432806811</v>
+        <v>0.6408186989654646</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398036585414677</v>
+        <v>0.6398033138035338</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423740387501233</v>
+        <v>0.6423724230720287</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432567758920695</v>
+        <v>0.6432558113575543</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413497786586015</v>
+        <v>0.6413488201625033</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384727141545467</v>
+        <v>0.6384717433462526</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403370388701133</v>
+        <v>0.6403341832166273</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404130756832165</v>
+        <v>0.6404103143497983</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639906366456132</v>
+        <v>0.639904935997314</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422810079685446</v>
+        <v>0.6422798562912841</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450225229731323</v>
+        <v>0.6450202952028378</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.646915200175425</v>
+        <v>0.6469122503511757</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465585366487903</v>
+        <v>0.6465560376828845</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646781587818212</v>
+        <v>0.6467801485737885</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455625432057093</v>
+        <v>0.6455601238594834</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450211670192215</v>
+        <v>0.6450169730731848</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458187383694669</v>
+        <v>0.6458115405104604</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435886246222791</v>
+        <v>0.6435792155026858</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6427361419720474</v>
+        <v>0.6427241676006776</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6438770727700349</v>
+        <v>0.643863312650005</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6444560178403261</v>
+        <v>0.6444414520953421</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.646244152886647</v>
+        <v>0.6462271809066067</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6529619595080214</v>
+        <v>0.6529477285781573</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6648585556326562</v>
+        <v>0.6648383649764198</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6721297497787881</v>
+        <v>0.6721071420648244</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6880356335415666</v>
+        <v>0.6880150666854277</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6971834457232227</v>
+        <v>0.6971679515172786</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6995478198187035</v>
+        <v>0.6995315781534255</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.69982344895825</v>
+        <v>0.6998068741253191</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080111548910795</v>
+        <v>0.7080063028573139</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.708048210144854</v>
+        <v>0.7080444366885139</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109083571069611</v>
+        <v>0.7109106852243594</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7173926977040803</v>
+        <v>0.7174074746013601</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7175803664230112</v>
+        <v>0.7175960949801916</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7247145242739723</v>
+        <v>0.7247363067651796</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.719969083772163</v>
+        <v>0.7199783237842416</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7233411623066804</v>
+        <v>0.7233517232675046</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228455334456783</v>
+        <v>0.7228545805601769</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199907404657977</v>
+        <v>0.7199980718102539</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714739015669722</v>
+        <v>0.7147391101074838</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166346170498397</v>
+        <v>0.7166359082499605</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166332243090622</v>
+        <v>0.7166363412359443</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153434047133549</v>
+        <v>0.7153468334618542</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130858537847449</v>
+        <v>0.7130881222999481</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106406872002868</v>
+        <v>0.7106441131801795</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106641660594385</v>
+        <v>0.7106680146472695</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084925875034762</v>
+        <v>0.7084985762574331</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7059644710525604</v>
+        <v>0.7059758132300822</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041077074076457</v>
+        <v>0.7041206483738296</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7032422887697998</v>
+        <v>0.7032538063515062</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027155749745505</v>
+        <v>0.7027236721581991</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032234801851862</v>
+        <v>0.7032251515121347</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049724224041251</v>
+        <v>0.7049656232497374</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7066169603077302</v>
+        <v>0.7065972203518337</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7089041234679162</v>
+        <v>0.7088743409711136</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7107033733537093</v>
+        <v>0.7106691209237019</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7105277472563598</v>
+        <v>0.7105474054232748</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7102372774678867</v>
+        <v>0.7102394120346497</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7102961701583077</v>
+        <v>0.7102729908625922</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7112002419438171</v>
+        <v>0.7111344078588857</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7133214376898012</v>
+        <v>0.713217436619964</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7179317808341756</v>
+        <v>0.717726369774343</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7223623720569323</v>
+        <v>0.7220332722063716</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7259735997548482</v>
+        <v>0.7255077652957297</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7284252553718917</v>
+        <v>0.7277710679607101</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7309210715700816</v>
+        <v>0.7299784730051414</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7350819523979273</v>
+        <v>0.7335908846543757</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7268407358130384</v>
+        <v>0.7253871484804715</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,15 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7222730597555926</v>
+        <v>0.7200376025944718</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>0.7092244775944719</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506041631072268</v>
+        <v>0.6506034577017291</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514106364411777</v>
+        <v>0.6514102636226242</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524692975310211</v>
+        <v>0.6524686609491355</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497269496991041</v>
+        <v>0.6497266803784192</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464264746471535</v>
+        <v>0.6464261850440813</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431359024517755</v>
+        <v>0.6431355834597342</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408186989654646</v>
+        <v>0.640818361234215</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398033138035338</v>
+        <v>0.6398029756647162</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423724230720287</v>
+        <v>0.6423708392161682</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432558113575543</v>
+        <v>0.643254865966257</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413488201625033</v>
+        <v>0.6413478806773107</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384717433462526</v>
+        <v>0.6384707917829642</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403341832166273</v>
+        <v>0.6403313840493341</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404103143497983</v>
+        <v>0.6404076072666081</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639904935997314</v>
+        <v>0.6399035334060995</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422798562912841</v>
+        <v>0.6422787276471978</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450202952028378</v>
+        <v>0.6450181115549605</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469122503511757</v>
+        <v>0.6469093581085158</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465560376828845</v>
+        <v>0.6465535871891065</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467801485737885</v>
+        <v>0.6467787373602358</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455601238594834</v>
+        <v>0.6455577517892528</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450169730731848</v>
+        <v>0.6450128616494452</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458115405104604</v>
+        <v>0.6458044832469657</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435792155026858</v>
+        <v>0.6435699898637687</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6427241676006776</v>
+        <v>0.6427124267486024</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.643863312650005</v>
+        <v>0.6438498201381334</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6444414520953421</v>
+        <v>0.6444271688540009</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6462271809066067</v>
+        <v>0.6462105384327596</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6529477285781573</v>
+        <v>0.652933776822989</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6648383649764198</v>
+        <v>0.6648185683411514</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6721071420648244</v>
+        <v>0.6720849759032905</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6880150666854277</v>
+        <v>0.6879948951018761</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6971679515172786</v>
+        <v>0.6971527541727923</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6995315781534255</v>
+        <v>0.6995156455850998</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6998068741253191</v>
+        <v>0.6997906112360186</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080063028573139</v>
+        <v>0.7080015363483187</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080444366885139</v>
+        <v>0.7080407266497206</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109106852243594</v>
+        <v>0.7109129578480047</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7174074746013601</v>
+        <v>0.7174219624835404</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7175960949801916</v>
+        <v>0.7176115183853994</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7247363067651796</v>
+        <v>0.7247576720269671</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7199783237842416</v>
+        <v>0.7199873859544283</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7233517232675046</v>
+        <v>0.7233620818840397</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228545805601769</v>
+        <v>0.7228634571143899</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7199980718102539</v>
+        <v>0.7200052670936639</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147391101074838</v>
+        <v>0.714739203607083</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166359082499605</v>
+        <v>0.7166371772112927</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166363412359443</v>
+        <v>0.716639399594136</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153468334618542</v>
+        <v>0.7153501961443559</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130881222999481</v>
+        <v>0.7130903442035876</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106441131801795</v>
+        <v>0.7106474664193211</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106680146472695</v>
+        <v>0.7106717816885889</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7084985762574331</v>
+        <v>0.7085044407572874</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7059758132300822</v>
+        <v>0.7059869355581856</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041206483738296</v>
+        <v>0.7041333486047234</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7032538063515062</v>
+        <v>0.7032651191285844</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027236721581991</v>
+        <v>0.7027316423019225</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032251515121347</v>
+        <v>0.7032268273011386</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049656232497374</v>
+        <v>0.7049589956965967</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7065972203518337</v>
+        <v>0.7065778824104387</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7088743409711136</v>
+        <v>0.7088451196853051</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7106691209237019</v>
+        <v>0.7106354833386402</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7105474054232748</v>
+        <v>0.7105771006333882</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7102394120346497</v>
+        <v>0.7102552497256013</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7102729908625922</v>
+        <v>0.7102663670462892</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7111344078588857</v>
+        <v>0.7110938543591059</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.713217436619964</v>
+        <v>0.713146035598227</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.717726369774343</v>
+        <v>0.7175671150587124</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7220332722063716</v>
+        <v>0.7217681811758861</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7255077652957297</v>
+        <v>0.7251258792866828</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7277710679607101</v>
+        <v>0.7272316106275973</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7299784730051414</v>
+        <v>0.7292102216085732</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7335908846543757</v>
+        <v>0.7323723695219997</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7253871484804715</v>
+        <v>0.7242947196439601</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7200376025944718</v>
+        <v>0.7186367696857554</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.7092244775944719</v>
+        <v>0.7078236446857555</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7105771006333882</v>
+        <v>0.7105271435065681</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7102552497256013</v>
+        <v>0.7101928243628093</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7102663670462892</v>
+        <v>0.7102006024685692</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7110938543591059</v>
+        <v>0.7110162171296854</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.713146035598227</v>
+        <v>0.7130576522448585</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7175671150587124</v>
+        <v>0.7174621700378209</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7217681811758861</v>
+        <v>0.7216426312160533</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7251258792866828</v>
+        <v>0.7249797341654716</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7272316106275973</v>
+        <v>0.7270550522683936</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7292102216085732</v>
+        <v>0.7289790987040041</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7323723695219997</v>
+        <v>0.7320792501174574</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7242947196439601</v>
+        <v>0.7238965353652517</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7186367696857554</v>
+        <v>0.717929313650459</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.7078236446857555</v>
+        <v>0.7071161886504591</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506034577017291</v>
+        <v>0.650602765992122</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514102636226242</v>
+        <v>0.6514098979559535</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524686609491355</v>
+        <v>0.6524680366689037</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497266803784192</v>
+        <v>0.649726416113406</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464261850440813</v>
+        <v>0.6464259008977171</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431355834597342</v>
+        <v>0.643135270498004</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640818361234215</v>
+        <v>0.6408180299000128</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398029756647162</v>
+        <v>0.6398026439374588</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423708392161682</v>
+        <v>0.6423692862517114</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643254865966257</v>
+        <v>0.6432539391540293</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413478806773107</v>
+        <v>0.6413469596431312</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384707917829642</v>
+        <v>0.6384698588981821</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403313840493341</v>
+        <v>0.6403286397091559</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404076072666081</v>
+        <v>0.640404952851113</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399035334060995</v>
+        <v>0.6399021578761802</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422787276471978</v>
+        <v>0.6422776213525141</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450181115549605</v>
+        <v>0.6450159707322191</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469093581085158</v>
+        <v>0.6469065217788734</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465535871891065</v>
+        <v>0.6465511837715654</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467787373602358</v>
+        <v>0.6467773533670714</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455577517892528</v>
+        <v>0.6455554256235705</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450128616494452</v>
+        <v>0.645008830337589</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6458044832469657</v>
+        <v>0.6457975625013974</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435699898637687</v>
+        <v>0.643560942394251</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6427124267486024</v>
+        <v>0.6427009126566575</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6438498201381334</v>
+        <v>0.6438365875112542</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6444271688540009</v>
+        <v>0.6444131599871119</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6462105384327596</v>
+        <v>0.6461942159754408</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.652933776822989</v>
+        <v>0.6529200961167039</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6648185683411514</v>
+        <v>0.6647991543199495</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6720849759032905</v>
+        <v>0.6720632385011085</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6879948951018761</v>
+        <v>0.6879751075227124</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6971527541727923</v>
+        <v>0.6971378452552707</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6995156455850998</v>
+        <v>0.6995000133942543</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6997906112360186</v>
+        <v>0.6997746515957537</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7080015363483187</v>
+        <v>0.7079968531506862</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080407266497206</v>
+        <v>0.7080370784841361</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109129578480047</v>
+        <v>0.7109151768695121</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7174219624835404</v>
+        <v>0.7174361697358939</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7176115183853994</v>
+        <v>0.7176266454178223</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7247576720269671</v>
+        <v>0.7247786319163946</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7199873859544283</v>
+        <v>0.719996275358692</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7233620818840397</v>
+        <v>0.7233722439031804</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228634571143899</v>
+        <v>0.7228721678713657</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200052670936639</v>
+        <v>0.7200123300539255</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714739203607083</v>
+        <v>0.7147392961697915</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166371772112927</v>
+        <v>0.7166384244940458</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.716639399594136</v>
+        <v>0.7166424010167669</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153501961443559</v>
+        <v>0.7153534946529604</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130903442035876</v>
+        <v>0.713092520915807</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106474664193211</v>
+        <v>0.7106507491944321</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106717816885889</v>
+        <v>0.7106754697306277</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085044407572874</v>
+        <v>0.7085101848081962</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7059869355581856</v>
+        <v>0.7059978443382158</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041333486047234</v>
+        <v>0.7041458147022243</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7032651191285844</v>
+        <v>0.7032762324327579</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027316423019225</v>
+        <v>0.7027394881988565</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032268273011386</v>
+        <v>0.7032285064274832</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049589956965967</v>
+        <v>0.704952533822258</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7065778824104387</v>
+        <v>0.706558934641258</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7088451196853051</v>
+        <v>0.7088164443215058</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7106354833386402</v>
+        <v>0.7106024448198749</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7105271435065681</v>
+        <v>0.7105332340439346</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7101928243628093</v>
+        <v>0.7101793875019806</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7102006024685692</v>
+        <v>0.7101638096775222</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7110162171296854</v>
+        <v>0.7109391485275813</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7130576522448585</v>
+        <v>0.7129444729340489</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7174621700378209</v>
+        <v>0.7172551460120717</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7216426312160533</v>
+        <v>0.7213232212674122</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7249797341654716</v>
+        <v>0.7245379776229314</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7270550522683936</v>
+        <v>0.7264506716248921</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7289790987040041</v>
+        <v>0.7281359860849896</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7320792501174574</v>
+        <v>0.7308114854527548</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7238965353652517</v>
+        <v>0.7227342635221472</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.717929313650459</v>
+        <v>0.7165349615760251</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.7071161886504591</v>
+        <v>0.7033443765796704</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650602765992122</v>
+        <v>0.6506020875833807</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514098979559535</v>
+        <v>0.6514095392373682</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524680366689037</v>
+        <v>0.6524674243371802</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649726416113406</v>
+        <v>0.6497261567632073</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464259008977171</v>
+        <v>0.6464256220554316</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643135270498004</v>
+        <v>0.6431349633973279</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408180299000128</v>
+        <v>0.6408177047829424</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398026439374588</v>
+        <v>0.6398023184412411</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423692862517114</v>
+        <v>0.6423677632837747</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432539391540293</v>
+        <v>0.6432530303786683</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413469596431312</v>
+        <v>0.6413460565218383</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384698588981821</v>
+        <v>0.6384689441474198</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403286397091559</v>
+        <v>0.6403259486013386</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.640404952851113</v>
+        <v>0.6404023495817155</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399021578761802</v>
+        <v>0.6399008086320492</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422776213525141</v>
+        <v>0.6422765367502474</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450159707322191</v>
+        <v>0.6450138714876699</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469065217788734</v>
+        <v>0.6469037397574853</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465511837715654</v>
+        <v>0.6465488260874261</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467773533670714</v>
+        <v>0.6467759958147408</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455554256235705</v>
+        <v>0.6455531440434946</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.645008830337589</v>
+        <v>0.6450048768201179</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457975625013974</v>
+        <v>0.6457907743522651</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.643560942394251</v>
+        <v>0.6435520679857496</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6427009126566575</v>
+        <v>0.6426896188238205</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6438365875112542</v>
+        <v>0.6438236073402406</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6444131599871119</v>
+        <v>0.644399417674014</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6461942159754408</v>
+        <v>0.6461782044053896</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6529200961167039</v>
+        <v>0.6529066786454569</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6647991543199495</v>
+        <v>0.6647801119414198</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6720632385011085</v>
+        <v>0.6720419175540049</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6879751075227124</v>
+        <v>0.6879556931033065</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6971378452552707</v>
+        <v>0.697123216646129</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6995000133942543</v>
+        <v>0.6994846731855153</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6997746515957537</v>
+        <v>0.6997589868289225</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079968531506862</v>
+        <v>0.707992251125573</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080370784841361</v>
+        <v>0.7080334906953918</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109151768695121</v>
+        <v>0.7109173440976007</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7174361697358939</v>
+        <v>0.7174501044228606</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7176266454178223</v>
+        <v>0.7176414845236812</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7247786319163946</v>
+        <v>0.7247991978461</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.719996275358692</v>
+        <v>0.7200049968820124</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7233722439031804</v>
+        <v>0.7233822148567409</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228721678713657</v>
+        <v>0.7228807174190266</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200123300539255</v>
+        <v>0.7200192642938434</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147392961697915</v>
+        <v>0.7147393877978099</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166384244940458</v>
+        <v>0.7166396506401609</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166424010167669</v>
+        <v>0.7166453470768902</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153534946529604</v>
+        <v>0.715356730808165</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.713092520915807</v>
+        <v>0.7130946537997167</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106507491944321</v>
+        <v>0.710653963688755</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106754697306277</v>
+        <v>0.7106790812162348</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085101848081962</v>
+        <v>0.708515812062301</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7059978443382158</v>
+        <v>0.706008545634098</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041458147022243</v>
+        <v>0.704158053031099</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7032762324327579</v>
+        <v>0.7032871514156067</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027394881988565</v>
+        <v>0.7027472125685721</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032285064274832</v>
+        <v>0.7032301878441629</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.704952533822258</v>
+        <v>0.7049462319601282</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.706558934641258</v>
+        <v>0.7065403656516899</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7088164443215058</v>
+        <v>0.7087883001252131</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7106024448198749</v>
+        <v>0.7105699900996438</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7105332340439346</v>
+        <v>0.7105400568666007</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7101793875019806</v>
+        <v>0.7101684323436684</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7101638096775222</v>
+        <v>0.7101329627471109</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7109391485275813</v>
+        <v>0.7108798643273657</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7129444729340489</v>
+        <v>0.7128517843585129</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7172551460120717</v>
+        <v>0.7170602965449697</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7213232212674122</v>
+        <v>0.7209893679780666</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7245379776229314</v>
+        <v>0.7240413927416026</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7264506716248921</v>
+        <v>0.7257468092729835</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7281359860849896</v>
+        <v>0.7271161427939233</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7308114854527548</v>
+        <v>0.7293142648718669</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7227342635221472</v>
+        <v>0.7211886116722164</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7165349615760251</v>
+        <v>0.7145004221461694</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.7033443765796704</v>
+        <v>0.7012317311563298</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506020875833807</v>
+        <v>0.6506014220955274</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514095392373682</v>
+        <v>0.651409187270739</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524674243371802</v>
+        <v>0.6524668236142075</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497261567632073</v>
+        <v>0.6497259021921442</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464256220554316</v>
+        <v>0.64642534837023</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431349633973279</v>
+        <v>0.6431346619947192</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408177047829424</v>
+        <v>0.640817385709768</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398023184412411</v>
+        <v>0.6398019990022525</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423677632837747</v>
+        <v>0.6423662694517038</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432530303786683</v>
+        <v>0.643252139118861</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413460565218383</v>
+        <v>0.6413451707960256</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384689441474198</v>
+        <v>0.6384680470071457</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403259486013386</v>
+        <v>0.6403233091923662</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6404023495817155</v>
+        <v>0.6403997959948492</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6399008086320492</v>
+        <v>0.639899484927545</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422765367502474</v>
+        <v>0.6422754732088998</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450138714876699</v>
+        <v>0.6450118126222903</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6469037397574853</v>
+        <v>0.646901010500376</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465488260874261</v>
+        <v>0.6465465128444133</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467759958147408</v>
+        <v>0.6467746639531562</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455531440434946</v>
+        <v>0.6455509057801025</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450048768201179</v>
+        <v>0.6450009988680152</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457907743522651</v>
+        <v>0.6457841150267793</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435520679857496</v>
+        <v>0.6435433617231854</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426896188238205</v>
+        <v>0.6426785389950145</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6438236073402406</v>
+        <v>0.643810872476158</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.644399417674014</v>
+        <v>0.644385934388094</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6461782044053896</v>
+        <v>0.6461624949368256</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6529066786454569</v>
+        <v>0.6528935168925581</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6647801119414198</v>
+        <v>0.6647614306491164</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6720419175540049</v>
+        <v>0.6720210012234191</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6879556931033065</v>
+        <v>0.6879366414029147</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.697123216646129</v>
+        <v>0.6971088605280669</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6994846731855153</v>
+        <v>0.6994696168727264</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6997589868289225</v>
+        <v>0.6997436088644752</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.707992251125573</v>
+        <v>0.7079877282056453</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080334906953918</v>
+        <v>0.7080299618333368</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109173440976007</v>
+        <v>0.7109194612625014</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7174501044228606</v>
+        <v>0.7174637743032257</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7176414845236812</v>
+        <v>0.7176560438318398</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7247991978461</v>
+        <v>0.7248193808048983</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200049968820124</v>
+        <v>0.7200135552272615</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7233822148567409</v>
+        <v>0.7233920000713996</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228807174190266</v>
+        <v>0.7228891101781171</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200192642938434</v>
+        <v>0.7200260732871517</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147393877978099</v>
+        <v>0.7147394784941775</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166396506401609</v>
+        <v>0.7166408561740294</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166453470768902</v>
+        <v>0.7166482392902177</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.715356730808165</v>
+        <v>0.7153599063622197</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130946537997167</v>
+        <v>0.7130967441642233</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710653963688755</v>
+        <v>0.7106571119967791</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106790812162348</v>
+        <v>0.7106826184891433</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.708515812062301</v>
+        <v>0.7085213260263087</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.706008545634098</v>
+        <v>0.7060190452833631</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.704158053031099</v>
+        <v>0.7041700697294357</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7032871514156067</v>
+        <v>0.7032978810559433</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027472125685721</v>
+        <v>0.7027548180590312</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032301878441629</v>
+        <v>0.7032318705767335</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049462319601282</v>
+        <v>0.7049400846863032</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7065403656516899</v>
+        <v>0.7065221644781576</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7087883001252131</v>
+        <v>0.7087606728540032</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7105699900996438</v>
+        <v>0.7105381044017802</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7105400568666007</v>
+        <v>0.7105578912681354</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7101684323436684</v>
+        <v>0.7101705522546709</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7101329627471109</v>
+        <v>0.7101165147025893</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7108798643273657</v>
+        <v>0.7108369406813611</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7128517843585129</v>
+        <v>0.7127809251503854</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7170602965449697</v>
+        <v>0.7168986366981768</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7209893679780666</v>
+        <v>0.7207066012380684</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7240413927416026</v>
+        <v>0.7236189404241593</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7257468092729835</v>
+        <v>0.7251525649863193</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7271161427939233</v>
+        <v>0.7262758646140079</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7293142648718669</v>
+        <v>0.7281016739385692</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7211886116722164</v>
+        <v>0.7200497132922515</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7145004221461694</v>
+        <v>0.7132463467742342</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.7012317311563298</v>
+        <v>0.7009118894330598</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B117"/>
+  <dimension ref="A1:B118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506014220955274</v>
+        <v>0.6506007691629205</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.651409187270739</v>
+        <v>0.6514088418672487</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524668236142075</v>
+        <v>0.6524662341729877</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497259021921442</v>
+        <v>0.649725652269479</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.64642534837023</v>
+        <v>0.646425079700493</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431346619947192</v>
+        <v>0.643134366133174</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640817385709768</v>
+        <v>0.6408170725136252</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398019990022525</v>
+        <v>0.6398016854530819</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423662694517038</v>
+        <v>0.6423648039274521</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.643252139118861</v>
+        <v>0.6432512648731865</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413451707960256</v>
+        <v>0.6413443019680179</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384680470071457</v>
+        <v>0.6384671669737823</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403233091923662</v>
+        <v>0.6403207200070493</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403997959948492</v>
+        <v>0.6403972906822395</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639899484927545</v>
+        <v>0.6398981860444756</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422754732088998</v>
+        <v>0.6422744301212372</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450118126222903</v>
+        <v>0.6450097929826992</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.646901010500376</v>
+        <v>0.6468983325215097</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465465128444133</v>
+        <v>0.6465442427984551</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467746639531562</v>
+        <v>0.6467733570603194</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455509057801025</v>
+        <v>0.6455487096121431</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6450009988680152</v>
+        <v>0.644997194336567</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457841150267793</v>
+        <v>0.6457775808938725</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435433617231854</v>
+        <v>0.6435348188757311</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426785389950145</v>
+        <v>0.6426676671495952</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.643810872476158</v>
+        <v>0.6437983760371918</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.644385934388094</v>
+        <v>0.6443727028831141</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6461624949368256</v>
+        <v>0.6461470791114685</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528935168925581</v>
+        <v>0.652880603624495</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6647614306491164</v>
+        <v>0.6647431002821319</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6720210012234191</v>
+        <v>0.6720004781147036</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6879366414029147</v>
+        <v>0.6879179423660802</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6971088605280669</v>
+        <v>0.6970947693712473</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6994696168727264</v>
+        <v>0.6994548366648776</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6997436088644752</v>
+        <v>0.6997285099222481</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079877282056453</v>
+        <v>0.7079832823921713</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080299618333368</v>
+        <v>0.7080264904923571</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109194612625014</v>
+        <v>0.7109215300200931</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7174637743032257</v>
+        <v>0.7174771868444465</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7176560438318398</v>
+        <v>0.7176703311685441</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7248193808048983</v>
+        <v>0.7248391913772447</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200135552272615</v>
+        <v>0.7200219549235971</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7233920000713996</v>
+        <v>0.7234016046780981</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228891101781171</v>
+        <v>0.7228973504097226</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200260732871517</v>
+        <v>0.7200327603842143</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147394784941775</v>
+        <v>0.7147395682626912</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166408561740294</v>
+        <v>0.716642041603178</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166482392902177</v>
+        <v>0.7166510791177034</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153599063622197</v>
+        <v>0.715363023002298</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130967441642233</v>
+        <v>0.7130987932666946</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106571119967791</v>
+        <v>0.7106601961286823</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106826184891433</v>
+        <v>0.7106860837989204</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085213260263087</v>
+        <v>0.7085267300686261</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060190452833631</v>
+        <v>0.7060293489075654</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041700697294357</v>
+        <v>0.7041818707185523</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7032978810559433</v>
+        <v>0.7033084261668385</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027548180590312</v>
+        <v>0.7027623072485143</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032318705767335</v>
+        <v>0.7032335537185288</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049400846863032</v>
+        <v>0.7049340868071847</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7065221644781576</v>
+        <v>0.7065043205665498</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7087606728540032</v>
+        <v>0.7087335487562039</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7105381044017802</v>
+        <v>0.7105067734232114</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7105578912681354</v>
+        <v>0.7105225088963406</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7101705522546709</v>
+        <v>0.7101609560442582</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7101165147025893</v>
+        <v>0.7100906962121513</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7108369406813611</v>
+        <v>0.7107986329060781</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7127809251503854</v>
+        <v>0.7126610785686633</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7168986366981768</v>
+        <v>0.7166749748604886</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7207066012380684</v>
+        <v>0.7203574080594959</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7236189404241593</v>
+        <v>0.7231308088016528</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7251525649863193</v>
+        <v>0.7244932389535736</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7262758646140079</v>
+        <v>0.7253901438368786</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7281016739385692</v>
+        <v>0.7268119365079573</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7200497132922515</v>
+        <v>0.7187673975475923</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7132463467742342</v>
+        <v>0.7117196769200467</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,15 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.7009118894330598</v>
+        <v>0.6996197268562429</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>0.6909197268562428</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506007691629205</v>
+        <v>0.6506001284335852</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514088418672487</v>
+        <v>0.6514085028450532</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524662341729877</v>
+        <v>0.6524656556986883</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649725652269479</v>
+        <v>0.6497254068691942</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.646425079700493</v>
+        <v>0.6464248159097349</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643134366133174</v>
+        <v>0.6431340756613987</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408170725136252</v>
+        <v>0.6408167650337322</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398016854530819</v>
+        <v>0.6398013776324276</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423648039274521</v>
+        <v>0.642363365914052</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432512648731865</v>
+        <v>0.6432504071591777</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413443019680179</v>
+        <v>0.6413434495589412</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384671669737823</v>
+        <v>0.6384663035627677</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403207200070493</v>
+        <v>0.6403181796257792</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403972906822395</v>
+        <v>0.6403948322883177</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398981860444756</v>
+        <v>0.6398969112913213</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422744301212372</v>
+        <v>0.6422734069031358</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450097929826992</v>
+        <v>0.6450078114590073</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468983325215097</v>
+        <v>0.6468957043900987</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465442427984551</v>
+        <v>0.6465420147514582</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467733570603194</v>
+        <v>0.6467720744410184</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455487096121431</v>
+        <v>0.6455465543638192</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.644997194336567</v>
+        <v>0.6449934611614152</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457775808938725</v>
+        <v>0.645771168457608</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435348188757311</v>
+        <v>0.6435264348882637</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426676671495952</v>
+        <v>0.6426569974904804</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437983760371918</v>
+        <v>0.6437861113962994</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6443727028831141</v>
+        <v>0.6443597161802919</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6461470791114685</v>
+        <v>0.6461319487834403</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.652880603624495</v>
+        <v>0.6528679318777362</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6647431002821319</v>
+        <v>0.6647251110567691</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6720004781147036</v>
+        <v>0.6719803372565385</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6879179423660802</v>
+        <v>0.6878995863050525</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970947693712473</v>
+        <v>0.6970809359202297</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6994548366648776</v>
+        <v>0.6994403250527942</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6997285099222481</v>
+        <v>0.6997136825000225</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079832823921713</v>
+        <v>0.7079789117522498</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080264904923571</v>
+        <v>0.7080230753097606</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109215300200931</v>
+        <v>0.7109235519557799</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7174771868444465</v>
+        <v>0.7174903492361807</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7176703311685441</v>
+        <v>0.7176843540713512</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7248391913772447</v>
+        <v>0.7248586397616401</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200219549235971</v>
+        <v>0.7200302003343932</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234016046780981</v>
+        <v>0.7234110336209297</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7228973504097226</v>
+        <v>0.7229054422223887</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200327603842143</v>
+        <v>0.7200393288174316</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147395682626912</v>
+        <v>0.7147396571078295</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.716642041603178</v>
+        <v>0.7166432074189245</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166510791177034</v>
+        <v>0.7166538679679938</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.715363023002298</v>
+        <v>0.7153660823534922</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7130987932666946</v>
+        <v>0.7131008023154675</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106601961286823</v>
+        <v>0.7106632180145098</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106860837989204</v>
+        <v>0.7106894793056275</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085267300686261</v>
+        <v>0.7085320274260827</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060293489075654</v>
+        <v>0.7060394619221365</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041818707185523</v>
+        <v>0.7041934617123962</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033084261668385</v>
+        <v>0.7033187914023193</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027623072485143</v>
+        <v>0.7027696826475172</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032335537185288</v>
+        <v>0.7032352364262088</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049340868071847</v>
+        <v>0.7049282333478259</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7065043205665498</v>
+        <v>0.7064868237536976</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7087335487562039</v>
+        <v>0.708706914550584</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7105067734232114</v>
+        <v>0.7104759833162198</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7105225088963406</v>
+        <v>0.7104876866647176</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7101609560442582</v>
+        <v>0.7100407930559726</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7100906962121513</v>
+        <v>0.7099355376090282</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7107986329060781</v>
+        <v>0.7106206199822361</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7126610785686633</v>
+        <v>0.7123801425119758</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7166749748604886</v>
+        <v>0.7162791403311922</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7203574080594959</v>
+        <v>0.7198222109623722</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7231308088016528</v>
+        <v>0.7224440251897899</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7244932389535736</v>
+        <v>0.7236135898998692</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7253901438368786</v>
+        <v>0.7242581594100668</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7268119365079573</v>
+        <v>0.7252437091202907</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7187673975475923</v>
+        <v>0.7171257653860796</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7117196769200467</v>
+        <v>0.70969269856538</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6996197268562429</v>
+        <v>0.6973487360120685</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6909197268562428</v>
+        <v>0.6886093610120685</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6506001284335852</v>
+        <v>0.6505994995685813</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514085028450532</v>
+        <v>0.6514081700289645</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524656556986883</v>
+        <v>0.6524650878880833</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497254068691942</v>
+        <v>0.649725165869781</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464248159097349</v>
+        <v>0.6464245568663729</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431340756613987</v>
+        <v>0.6431337904335545</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408167650337322</v>
+        <v>0.6408164631151146</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398013776324276</v>
+        <v>0.6398010753848205</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642363365914052</v>
+        <v>0.6423619546441692</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432504071591777</v>
+        <v>0.6432495655124335</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413434495589412</v>
+        <v>0.6413426131078415</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384663035627677</v>
+        <v>0.6384654563076647</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403181796257792</v>
+        <v>0.6403156866819351</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403948322883177</v>
+        <v>0.6403924195077798</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398969112913213</v>
+        <v>0.6398956600020085</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422734069031358</v>
+        <v>0.642272402992494</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450078114590073</v>
+        <v>0.6450058669827871</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468957043900987</v>
+        <v>0.6468931247280614</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465420147514582</v>
+        <v>0.6465398275492046</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467720744410184</v>
+        <v>0.6467708154255989</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455465543638192</v>
+        <v>0.6455444389026946</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449934611614152</v>
+        <v>0.6449897973548323</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.645771168457608</v>
+        <v>0.6457648743509564</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435264348882637</v>
+        <v>0.6435182053732877</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426569974904804</v>
+        <v>0.6426465244338757</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437861113962994</v>
+        <v>0.6437740721695402</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6443597161802919</v>
+        <v>0.6443469675560897</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6461319487834403</v>
+        <v>0.6461170961049936</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528679318777362</v>
+        <v>0.6528554949462644</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6647251110567691</v>
+        <v>0.6647074535492195</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6719803372565385</v>
+        <v>0.671960568081478</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6878995863050525</v>
+        <v>0.6878815638831584</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970809359202297</v>
+        <v>0.6970673531816064</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6994403250527942</v>
+        <v>0.6994260747965375</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6997136825000225</v>
+        <v>0.6996991193612678</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079789117522498</v>
+        <v>0.7079746144161696</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080230753097606</v>
+        <v>0.7080197149642264</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109235519557799</v>
+        <v>0.7109255285881356</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7174903492361807</v>
+        <v>0.7175032684030695</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7176843540713512</v>
+        <v>0.7176981198022968</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7248586397616401</v>
+        <v>0.7248777357880389</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200302003343932</v>
+        <v>0.7200382956647453</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234110336209297</v>
+        <v>0.7234202916655489</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229054422223887</v>
+        <v>0.722913389578864</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200393288174316</v>
+        <v>0.7200457817063626</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147396571078295</v>
+        <v>0.7147397450346844</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166432074189245</v>
+        <v>0.7166443540970038</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166538679679938</v>
+        <v>0.7166566071997424</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153660823534922</v>
+        <v>0.7153690859816431</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131008023154675</v>
+        <v>0.7131027724722123</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106632180145098</v>
+        <v>0.7106661795081092</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106894793056275</v>
+        <v>0.7106928070842066</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085320274260827</v>
+        <v>0.7085372212102639</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060394619221365</v>
+        <v>0.7060493895457032</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7041934617123962</v>
+        <v>0.7042048482264627</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033187914023193</v>
+        <v>0.7033289812637504</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027696826475172</v>
+        <v>0.7027769467006133</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032352364262088</v>
+        <v>0.7032369179156192</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049282333478259</v>
+        <v>0.7049225195409583</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7064868237536976</v>
+        <v>0.706469664249828</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.708706914550584</v>
+        <v>0.7086807574070072</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7104759833162198</v>
+        <v>0.7104457206714327</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7104876866647176</v>
+        <v>0.7104534121261816</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7100407930559726</v>
+        <v>0.7098110125506171</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7099355376090282</v>
+        <v>0.7096507845766051</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7106206199822361</v>
+        <v>0.7103028091421594</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7123801425119758</v>
+        <v>0.7119854544290327</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7162791403311922</v>
+        <v>0.7157458655941005</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7198222109623722</v>
+        <v>0.7191269136956483</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7224440251897899</v>
+        <v>0.721576094305006</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7236135898998692</v>
+        <v>0.7225241986381969</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7242581594100668</v>
+        <v>0.7228838866283226</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7252437091202907</v>
+        <v>0.7233898380570793</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7171257653860796</v>
+        <v>0.7151142413255416</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.70969269856538</v>
+        <v>0.7071646311661441</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6973487360120685</v>
+        <v>0.6942536314973099</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6886093610120685</v>
+        <v>0.6799631135303663</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505994995685813</v>
+        <v>0.6505988822414046</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514081700289645</v>
+        <v>0.6514078432501468</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524650878880833</v>
+        <v>0.6524645304490221</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649725165869781</v>
+        <v>0.6497249291540395</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464245568663729</v>
+        <v>0.6464243024435089</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431337904335545</v>
+        <v>0.643133510309012</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408164631151146</v>
+        <v>0.6408161666083466</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398010753848205</v>
+        <v>0.6398007785603629</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423619546441692</v>
+        <v>0.6423605693787399</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432495655124335</v>
+        <v>0.6432487394857818</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413426131078415</v>
+        <v>0.6413417921708564</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384654563076647</v>
+        <v>0.6384646247593219</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403156866819351</v>
+        <v>0.6403132398594354</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403924195077798</v>
+        <v>0.6403900510832778</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398956600020085</v>
+        <v>0.6398944315347483</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.642272402992494</v>
+        <v>0.6422714178482039</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450058669827871</v>
+        <v>0.6450039585251548</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468931247280614</v>
+        <v>0.6468905922076187</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465398275492046</v>
+        <v>0.6465376800793614</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467708154255989</v>
+        <v>0.6467695793688002</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455444389026946</v>
+        <v>0.6455423621377147</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449897973548323</v>
+        <v>0.6449862010021988</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457648743509564</v>
+        <v>0.6457586953299101</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435182053732877</v>
+        <v>0.6435101261032999</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426465244338757</v>
+        <v>0.6426362425995624</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437740721695402</v>
+        <v>0.6437622522050406</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6443469675560897</v>
+        <v>0.644334450530665</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6461170961049936</v>
+        <v>0.646102513513015</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528554949462644</v>
+        <v>0.6528432863697955</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6647074535492195</v>
+        <v>0.6646901186791858</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.671960568081478</v>
+        <v>0.6719411604075585</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6878815638831584</v>
+        <v>0.6878638660990642</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970673531816064</v>
+        <v>0.6970540144123002</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6994260747965375</v>
+        <v>0.6994120789134739</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996991193612678</v>
+        <v>0.6996848135235224</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079746144161696</v>
+        <v>0.7079703885748914</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080197149642264</v>
+        <v>0.708016408174317</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109255285881356</v>
+        <v>0.7109274613723252</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175032684030695</v>
+        <v>0.7175159510168221</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7176981198022968</v>
+        <v>0.7177116353603474</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7248777357880389</v>
+        <v>0.724896488934326</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200382956647453</v>
+        <v>0.7200462449685681</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234202916655489</v>
+        <v>0.7234293834071313</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.722913389578864</v>
+        <v>0.7229211963024889</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200457817063626</v>
+        <v>0.720052122062587</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147397450346844</v>
+        <v>0.7147398320488987</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166443540970038</v>
+        <v>0.7166454820981651</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166566071997424</v>
+        <v>0.7166592981238075</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153690859816431</v>
+        <v>0.7153720353960173</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131027724722123</v>
+        <v>0.7131047048541612</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106661795081092</v>
+        <v>0.710669082390834</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106928070842066</v>
+        <v>0.7106960691286104</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085372212102639</v>
+        <v>0.7085423144134857</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060493895457032</v>
+        <v>0.7060591368089086</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042048482264627</v>
+        <v>0.7042160355862631</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033289812637504</v>
+        <v>0.70333900010592</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027769467006133</v>
+        <v>0.7027841017882817</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032369179156192</v>
+        <v>0.7032385974579347</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049225195409583</v>
+        <v>0.7049169408166533</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.706469664249828</v>
+        <v>0.7064528326219297</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7086807574070072</v>
+        <v>0.7086550649279975</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7104457206714327</v>
+        <v>0.7104159725015087</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7104534121261816</v>
+        <v>0.7104196731698178</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7098110125506171</v>
+        <v>0.7095917376490181</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7096507845766051</v>
+        <v>0.7093937615887822</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7103028091421594</v>
+        <v>0.7100098575040874</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7119854544290327</v>
+        <v>0.7116184792670047</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7157458655941005</v>
+        <v>0.7152595082426847</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7191269136956483</v>
+        <v>0.718495467123453</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.721576094305006</v>
+        <v>0.7207870895698825</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7225241986381969</v>
+        <v>0.7215330810015289</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7228838866283226</v>
+        <v>0.7216357771928295</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7233898380570793</v>
+        <v>0.7217183653305862</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7151142413255416</v>
+        <v>0.7133400736322901</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7071646311661441</v>
+        <v>0.7050402469070951</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6942536314973099</v>
+        <v>0.6919323621401565</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6799631135303663</v>
+        <v>0.6774427836868993</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7095917376490181</v>
+        <v>0.7096077928515084</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7093937615887822</v>
+        <v>0.7094125878871368</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7100098575040874</v>
+        <v>0.7100342048177672</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7116184792670047</v>
+        <v>0.7116445844773643</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7152595082426847</v>
+        <v>0.7152880290560439</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.718495467123453</v>
+        <v>0.7185266936141603</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7207870895698825</v>
+        <v>0.720820997629424</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7215330810015289</v>
+        <v>0.7215715657466562</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7216357771928295</v>
+        <v>0.7216804609953493</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7217183653305862</v>
+        <v>0.7217736589303068</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7133400736322901</v>
+        <v>0.7134090312922474</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7050402469070951</v>
+        <v>0.7051380050196605</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6919323621401565</v>
+        <v>0.6920911261452184</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6774427836868993</v>
+        <v>0.6777955827677229</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505988822414046</v>
+        <v>0.650598276137422</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514078432501468</v>
+        <v>0.6514075223458328</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524645304490221</v>
+        <v>0.6524639830999285</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497249291540395</v>
+        <v>0.6497246966088902</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464243024435089</v>
+        <v>0.6464240525187235</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.643133510309012</v>
+        <v>0.6431332351521228</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408161666083466</v>
+        <v>0.6408158753693041</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398007785603629</v>
+        <v>0.6398004870144826</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423605693787399</v>
+        <v>0.6423592094056797</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432487394857818</v>
+        <v>0.6432479286484873</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413417921708564</v>
+        <v>0.6413409863204292</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384646247593219</v>
+        <v>0.6384638084850808</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403132398594354</v>
+        <v>0.6403108378904248</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403900510832778</v>
+        <v>0.6403877258032399</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398944315347483</v>
+        <v>0.6398932252709426</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422714178482039</v>
+        <v>0.6422704509491814</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450039585251548</v>
+        <v>0.6450020850949597</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468905922076187</v>
+        <v>0.6468881055490218</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465376800793614</v>
+        <v>0.6465355712696003</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467695793688002</v>
+        <v>0.6467683656486553</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455423621377147</v>
+        <v>0.6455403230173329</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449862010021988</v>
+        <v>0.6449826702586756</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457586953299101</v>
+        <v>0.6457526282679167</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435101261032999</v>
+        <v>0.6435021930035666</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426362425995624</v>
+        <v>0.6426261468017119</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437622522050406</v>
+        <v>0.6437506455725545</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.644334450530665</v>
+        <v>0.6443221588569408</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.646102513513015</v>
+        <v>0.6460881937162539</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528432863697955</v>
+        <v>0.6528312999226344</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6646901186791858</v>
+        <v>0.6646730976943911</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6719411604075585</v>
+        <v>0.6719221044209024</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6878638660990642</v>
+        <v>0.6878464842718793</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970540144123002</v>
+        <v>0.6970409131084843</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6994120789134739</v>
+        <v>0.6993983306669711</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996848135235224</v>
+        <v>0.6996707582473805</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079703885748914</v>
+        <v>0.7079662324776475</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.708016408174317</v>
+        <v>0.7080131536970485</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109274613723252</v>
+        <v>0.7109293517033211</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175159510168221</v>
+        <v>0.7175284035076452</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177116353603474</v>
+        <v>0.7177249074931891</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.724896488934326</v>
+        <v>0.7249149083419177</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200462449685681</v>
+        <v>0.7200540521553181</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234293834071313</v>
+        <v>0.7234383132779136</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229211963024889</v>
+        <v>0.7229288660832547</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.720052122062587</v>
+        <v>0.720058352794317</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147398320488987</v>
+        <v>0.7147399181566074</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166454820981651</v>
+        <v>0.7166465918687456</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166592981238075</v>
+        <v>0.7166619420053317</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153720353960173</v>
+        <v>0.7153749320518419</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131047048541612</v>
+        <v>0.7131066005362103</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710669082390834</v>
+        <v>0.7106719283750378</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106960691286104</v>
+        <v>0.7106992673556987</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085423144134857</v>
+        <v>0.7085473099144306</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060591368089086</v>
+        <v>0.706068708562767</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042160355862631</v>
+        <v>0.704227028935366</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.70333900010592</v>
+        <v>0.7033488521428436</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027841017882817</v>
+        <v>0.7027911502286972</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032385974579347</v>
+        <v>0.7032402743760678</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049169408166533</v>
+        <v>0.7049114927925779</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7064528326219297</v>
+        <v>0.7064363197779859</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7086550649279975</v>
+        <v>0.7086298251311731</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7104159725015087</v>
+        <v>0.7103867262254983</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7104196731698178</v>
+        <v>0.7103864580111692</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7096077928515084</v>
+        <v>0.7094137853270351</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7094125878871368</v>
+        <v>0.7091851821729085</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7100342048177672</v>
+        <v>0.7097777140298878</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7116445844773643</v>
+        <v>0.7113190076124909</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7152880290560439</v>
+        <v>0.7148513456682786</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7185266936141603</v>
+        <v>0.7179557948165535</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.720820997629424</v>
+        <v>0.7201045709232081</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7215715657466562</v>
+        <v>0.7206724586452533</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7216804609953493</v>
+        <v>0.7205532204690841</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7217736589303068</v>
+        <v>0.7202769173562606</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7134090312922474</v>
+        <v>0.7118588713905121</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7051380050196605</v>
+        <v>0.7033701092321094</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6920911261452184</v>
+        <v>0.6903643990255012</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6777955827677229</v>
+        <v>0.6764961808608617</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650598276137422</v>
+        <v>0.6505976809533377</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514075223458328</v>
+        <v>0.6514072071590534</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524639830999285</v>
+        <v>0.652463445569327</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497246966088902</v>
+        <v>0.6497244681251938</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464240525187235</v>
+        <v>0.6464238069738797</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431332351521228</v>
+        <v>0.6431329648319994</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408158753693041</v>
+        <v>0.640815589258932</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398004870144826</v>
+        <v>0.6398002006076964</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423592094056797</v>
+        <v>0.6423578740386647</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432479286484873</v>
+        <v>0.6432471325855048</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413409863204292</v>
+        <v>0.6413401951445677</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384638084850808</v>
+        <v>0.6384630070680256</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403108378904248</v>
+        <v>0.640308479553083</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403877258032399</v>
+        <v>0.6403854424998046</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398932252709426</v>
+        <v>0.6398920406141442</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422704509491814</v>
+        <v>0.6422695017934485</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450020850949597</v>
+        <v>0.64500024573707</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468881055490218</v>
+        <v>0.6468856635184004</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465355712696003</v>
+        <v>0.6465335000858163</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467683656486553</v>
+        <v>0.6467671736654499</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455403230173329</v>
+        <v>0.6455383205277415</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449826702586756</v>
+        <v>0.6449792033460546</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457526282679167</v>
+        <v>0.6457466701506149</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435021930035666</v>
+        <v>0.6434944021452891</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426261468017119</v>
+        <v>0.6426162320401908</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437506455725545</v>
+        <v>0.6437392465535803</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6443221588569408</v>
+        <v>0.6443100865102599</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460881937162539</v>
+        <v>0.6460741296832309</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528312999226344</v>
+        <v>0.6528195296031349</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6646730976943911</v>
+        <v>0.664656382155917</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6719221044209024</v>
+        <v>0.6719033906592538</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6878464842718793</v>
+        <v>0.6878294100270416</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970409131084843</v>
+        <v>0.6970280429950821</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993983306669711</v>
+        <v>0.699384823555684</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996707582473805</v>
+        <v>0.6996569470260396</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079662324776475</v>
+        <v>0.7079621444296513</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080131536970485</v>
+        <v>0.7080099503265191</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109293517033211</v>
+        <v>0.7109312009189288</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175284035076452</v>
+        <v>0.7175406320750594</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177249074931891</v>
+        <v>0.7177379427083831</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7249149083419177</v>
+        <v>0.7249330028305425</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200540521553181</v>
+        <v>0.7200617209963607</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234383132779136</v>
+        <v>0.7234470855543353</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229288660832547</v>
+        <v>0.722936402483547</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.720058352794317</v>
+        <v>0.7200644767107762</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147399181566074</v>
+        <v>0.7147400033643861</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166465918687456</v>
+        <v>0.7166476838412144</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166619420053317</v>
+        <v>0.716664540065716</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153749320518419</v>
+        <v>0.715377777352702</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131066005362103</v>
+        <v>0.7131084605529033</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106719283750378</v>
+        <v>0.7106747191073659</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106992673556987</v>
+        <v>0.7107024036089099</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085473099144306</v>
+        <v>0.7085522104834685</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.706068708562767</v>
+        <v>0.7060781094865747</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.704227028935366</v>
+        <v>0.7042378332430373</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033488521428436</v>
+        <v>0.7033585414533017</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027911502286972</v>
+        <v>0.7027980942794817</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032402743760678</v>
+        <v>0.7032419480413221</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049114927925779</v>
+        <v>0.7049061712648061</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7064363197779859</v>
+        <v>0.7064201169520166</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7086298251311731</v>
+        <v>0.7086050264324976</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7103867262254983</v>
+        <v>0.7103579696538427</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7103864580111692</v>
+        <v>0.7103537551827553</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7094137853270351</v>
+        <v>0.7091723247017763</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7091851821729085</v>
+        <v>0.7089030231612485</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7097777140298878</v>
+        <v>0.7094616662631767</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7113190076124909</v>
+        <v>0.7109302226779605</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7148513456682786</v>
+        <v>0.7143533169653338</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7179557948165535</v>
+        <v>0.717322978387954</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7201045709232081</v>
+        <v>0.7193255569919111</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7206724586452533</v>
+        <v>0.7197083839394554</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7205532204690841</v>
+        <v>0.7193596053119446</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7202769173562606</v>
+        <v>0.7187165059188811</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7118588713905121</v>
+        <v>0.7102278829698889</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7033701092321094</v>
+        <v>0.7015102110849073</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6903643990255012</v>
+        <v>0.6884816625919643</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6764961808608617</v>
+        <v>0.6747548591683246</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B118"/>
+  <dimension ref="A1:B119"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505976809533377</v>
+        <v>0.6505970963966856</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514072071590534</v>
+        <v>0.6514068975383807</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.652463445569327</v>
+        <v>0.6524629175953938</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497244681251938</v>
+        <v>0.6497242435975829</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464238069738797</v>
+        <v>0.6464235656949381</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431329648319994</v>
+        <v>0.6431326992223099</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640815589258932</v>
+        <v>0.640815308143024</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398002006076964</v>
+        <v>0.6397999192053907</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423578740386647</v>
+        <v>0.6423565626159765</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432471325855048</v>
+        <v>0.6432463508967696</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413401951445677</v>
+        <v>0.6413394182461423</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384630070680256</v>
+        <v>0.6384622201062735</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640308479553083</v>
+        <v>0.6403061636695576</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403854424998046</v>
+        <v>0.6403832000468694</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398920406141442</v>
+        <v>0.6398908769890754</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422695017934485</v>
+        <v>0.642268569897266</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.64500024573707</v>
+        <v>0.6449984395307526</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468856635184004</v>
+        <v>0.6468832649257266</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465335000858163</v>
+        <v>0.6465314655304393</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467671736654499</v>
+        <v>0.6467660028407365</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455383205277415</v>
+        <v>0.6455363536911933</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449792033460546</v>
+        <v>0.6449757985497803</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457466701506149</v>
+        <v>0.6457408180708484</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434944021452891</v>
+        <v>0.6434867497391327</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426162320401908</v>
+        <v>0.6426064934923291</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437392465535803</v>
+        <v>0.6437280496320043</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6443100865102599</v>
+        <v>0.6442982276785844</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460741296832309</v>
+        <v>0.6460603146307862</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528195296031349</v>
+        <v>0.6528079696237192</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.664656382155917</v>
+        <v>0.6646399639243196</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6719033906592538</v>
+        <v>0.6718850099963882</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6878294100270416</v>
+        <v>0.6878126352829445</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970280429950821</v>
+        <v>0.6970153980158158</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.699384823555684</v>
+        <v>0.6993715513033942</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996569470260396</v>
+        <v>0.6996433735753873</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079621444296513</v>
+        <v>0.7079581227899128</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080099503265191</v>
+        <v>0.7080067968925913</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109312009189288</v>
+        <v>0.7109330103026357</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175406320750594</v>
+        <v>0.7175526426981405</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177379427083831</v>
+        <v>0.7177507472839387</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7249330028305425</v>
+        <v>0.72495078091225</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200617209963607</v>
+        <v>0.7200692551310037</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234470855543353</v>
+        <v>0.7234557043638123</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.722936402483547</v>
+        <v>0.7229438089435998</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200644767107762</v>
+        <v>0.7200704965263613</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147400033643861</v>
+        <v>0.7147400876792017</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166476838412144</v>
+        <v>0.7166487584346972</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.716664540065716</v>
+        <v>0.7166670934844912</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.715377777352702</v>
+        <v>0.7153805726528114</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131084605529033</v>
+        <v>0.7131102859003061</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106747191073659</v>
+        <v>0.7106774561718638</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107024036089099</v>
+        <v>0.7107054796617283</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085522104834685</v>
+        <v>0.7085570187876824</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060781094865747</v>
+        <v>0.7060873440954116</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042378332430373</v>
+        <v>0.7042484533115022</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033585414533017</v>
+        <v>0.7033680719861231</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027980942794817</v>
+        <v>0.7028049361394154</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032419480413221</v>
+        <v>0.7032436178702725</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049061712648061</v>
+        <v>0.7049009721991502</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7064201169520166</v>
+        <v>0.7064042156898848</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7086050264324976</v>
+        <v>0.7085806576303126</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7103579696538427</v>
+        <v>0.7103296909739895</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7103537551827553</v>
+        <v>0.7103215535248226</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7091723247017763</v>
+        <v>0.7091463750921934</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7089030231612485</v>
+        <v>0.7086652676402287</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7094616662631767</v>
+        <v>0.7091686914431083</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7109302226779605</v>
+        <v>0.7105842227792967</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7143533169653338</v>
+        <v>0.713801267099111</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.717322978387954</v>
+        <v>0.7166460864688489</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7193255569919111</v>
+        <v>0.7185179414899554</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7197083839394554</v>
+        <v>0.7187358954110188</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7193596053119446</v>
+        <v>0.7181793650809787</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7187165059188811</v>
+        <v>0.7172690191205497</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7102278829698889</v>
+        <v>0.7086632886109228</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.7015102110849073</v>
+        <v>0.6997626995033872</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6884816625919643</v>
+        <v>0.686744584029285</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,15 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6747548591683246</v>
+        <v>0.6731380255900565</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>0.6623249005900567</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505970963966856</v>
+        <v>0.6505965221853514</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514068975383807</v>
+        <v>0.6514065933376871</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524629175953938</v>
+        <v>0.652462398925532</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497242435975829</v>
+        <v>0.6497240229242983</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464235656949381</v>
+        <v>0.6464233285717811</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431326992223099</v>
+        <v>0.6431324382010798</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640815308143024</v>
+        <v>0.6408150318920128</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397999192053907</v>
+        <v>0.639799642677609</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423565626159765</v>
+        <v>0.6423552744994094</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432463508967696</v>
+        <v>0.6432455831965288</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413394182461423</v>
+        <v>0.6413386552422213</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384622201062735</v>
+        <v>0.6384614472123038</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403061636695576</v>
+        <v>0.6403038891040029</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403832000468694</v>
+        <v>0.6403809973582417</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398908769890754</v>
+        <v>0.6398897338406964</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.642268569897266</v>
+        <v>0.6422676547943134</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449984395307526</v>
+        <v>0.6449966655881383</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468832649257266</v>
+        <v>0.6468809086228857</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465314655304393</v>
+        <v>0.6465294666408361</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467660028407365</v>
+        <v>0.6467648526164006</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455363536911933</v>
+        <v>0.6455344215644132</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449757985497803</v>
+        <v>0.6449724542161255</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457408180708484</v>
+        <v>0.6457350692239427</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434867497391327</v>
+        <v>0.6434792321290956</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426064934923291</v>
+        <v>0.6425969265051225</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437280496320043</v>
+        <v>0.6437170494852322</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442982276785844</v>
+        <v>0.6442865767532082</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460603146307862</v>
+        <v>0.6460467420132276</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528079696237192</v>
+        <v>0.6527966144014284</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6646399639243196</v>
+        <v>0.6646238351464778</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6718850099963882</v>
+        <v>0.6718669536273458</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6878126352829445</v>
+        <v>0.6877961522382554</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970153980158158</v>
+        <v>0.6970029723237683</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993715513033942</v>
+        <v>0.6993585078493698</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996433735753873</v>
+        <v>0.6996300318245835</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079581227899128</v>
+        <v>0.7079541659691521</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080067968925913</v>
+        <v>0.7080036922596259</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109330103026357</v>
+        <v>0.7109347810862905</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175526426981405</v>
+        <v>0.7175644411452198</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177507472839387</v>
+        <v>0.7177633272783303</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.72495078091225</v>
+        <v>0.7249682508046948</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200692551310037</v>
+        <v>0.7200766580722175</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234557043638123</v>
+        <v>0.7234641736911572</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229438089435998</v>
+        <v>0.7229510887866691</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200704965263613</v>
+        <v>0.7200764148645913</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147400876792017</v>
+        <v>0.7147401711083683</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166487584346972</v>
+        <v>0.7166498160554748</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166670934844912</v>
+        <v>0.716669603401095</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153805726528114</v>
+        <v>0.7153833192591669</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131102859003061</v>
+        <v>0.7131120775377768</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106774561718638</v>
+        <v>0.7106801410929087</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107054796617283</v>
+        <v>0.7107084972209539</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085570187876824</v>
+        <v>0.708561737395618</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060873440954116</v>
+        <v>0.7060964167472537</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042484533115022</v>
+        <v>0.7042588937828509</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033680719861231</v>
+        <v>0.7033774475652279</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028049361394154</v>
+        <v>0.7028116779501081</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032436178702725</v>
+        <v>0.7032452833218559</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7049009721991502</v>
+        <v>0.7048958917229783</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7064042156898848</v>
+        <v>0.7063886078358252</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7085806576303126</v>
+        <v>0.7085567078901058</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7103296909739895</v>
+        <v>0.7103018787365961</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7103215535248226</v>
+        <v>0.7102898421763288</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7091463750921934</v>
+        <v>0.7091207604950014</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7086652676402287</v>
+        <v>0.7083434553690398</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7091686914431083</v>
+        <v>0.70877900499945</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7105842227792967</v>
+        <v>0.7101273427986704</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.713801267099111</v>
+        <v>0.7131249395287957</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7166460864688489</v>
+        <v>0.7158293283008761</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7185179414899554</v>
+        <v>0.7175510747632949</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7187358954110188</v>
+        <v>0.7175742751165202</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7181793650809787</v>
+        <v>0.7167709518710637</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7172690191205497</v>
+        <v>0.7155442444775933</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7086632886109228</v>
+        <v>0.7067028438635947</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6997626995033872</v>
+        <v>0.6974588247611119</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.686744584029285</v>
+        <v>0.6841413532028481</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6731380255900565</v>
+        <v>0.6699996510968734</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6623249005900567</v>
+        <v>0.6591865260968736</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7083434553690398</v>
+        <v>0.7083119828193873</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.70877900499945</v>
+        <v>0.7087432072471713</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7101273427986704</v>
+        <v>0.7100872029130363</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7131249395287957</v>
+        <v>0.7131336393572942</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7158293283008761</v>
+        <v>0.7158256747533484</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7175510747632949</v>
+        <v>0.7175388440928139</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7175742751165202</v>
+        <v>0.7175572378340175</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7167709518710637</v>
+        <v>0.7167530877766219</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7155442444775933</v>
+        <v>0.7155288091812495</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7067028438635947</v>
+        <v>0.7067064600339535</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6974588247611119</v>
+        <v>0.6974814867950595</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6841413532028481</v>
+        <v>0.6842005154363927</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6699996510968734</v>
+        <v>0.6701341139244907</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6591865260968736</v>
+        <v>0.6593209889244909</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505965221853514</v>
+        <v>0.6505959580471182</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514065933376871</v>
+        <v>0.6514062944159147</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.652462398925532</v>
+        <v>0.6524618893159676</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497240229242983</v>
+        <v>0.6497238060070384</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464233285717811</v>
+        <v>0.6464230954980446</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431324382010798</v>
+        <v>0.6431321816505078</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408150318920128</v>
+        <v>0.6408147603807716</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.639799642677609</v>
+        <v>0.6397993708988536</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423552744994094</v>
+        <v>0.6423540090732363</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432455831965288</v>
+        <v>0.6432448291127074</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413386552422213</v>
+        <v>0.6413379057634438</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384614472123038</v>
+        <v>0.6384606880123218</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403038891040029</v>
+        <v>0.6403016547607244</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403809973582417</v>
+        <v>0.6403788333858853</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398897338406964</v>
+        <v>0.6398886106333241</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422676547943134</v>
+        <v>0.6422667560349113</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449966655881383</v>
+        <v>0.6449949230527698</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468809086228857</v>
+        <v>0.6468785935018484</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465294666408361</v>
+        <v>0.6465275024877959</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467648526164006</v>
+        <v>0.6467637224537756</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455344215644132</v>
+        <v>0.6455325232370936</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449724542161255</v>
+        <v>0.6449691687495223</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457350692239427</v>
+        <v>0.6457294209032323</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434792321290956</v>
+        <v>0.6434718457867006</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425969265051225</v>
+        <v>0.6425875265878411</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437170494852322</v>
+        <v>0.6437062409757851</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442865767532082</v>
+        <v>0.6442751283199529</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460467420132276</v>
+        <v>0.6460334055120414</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527966144014284</v>
+        <v>0.6527854585489661</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6646238351464778</v>
+        <v>0.6646079882431276</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6718669536273458</v>
+        <v>0.6718492130544327</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6877961522382554</v>
+        <v>0.6877799533598872</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970029723237683</v>
+        <v>0.6969907602724287</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993585078493698</v>
+        <v>0.6993456873392159</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996300318245835</v>
+        <v>0.6996169159071171</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079541659691521</v>
+        <v>0.7079502724278092</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080036922596259</v>
+        <v>0.7080006353252685</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109347810862905</v>
+        <v>0.7109365144526305</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175644411452198</v>
+        <v>0.7175760329830779</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177633272783303</v>
+        <v>0.7177756885399948</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7249682508046948</v>
+        <v>0.7249854204437395</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200766580722175</v>
+        <v>0.7200839332120619</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234641736911572</v>
+        <v>0.7234724973846745</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229510887866691</v>
+        <v>0.7229582452239509</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200764148645913</v>
+        <v>0.7200822342618671</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147401711083683</v>
+        <v>0.7147402536595063</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166498160554748</v>
+        <v>0.7166508570974626</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.716669603401095</v>
+        <v>0.7166720709165593</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153833192591669</v>
+        <v>0.7153860184335882</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131120775377768</v>
+        <v>0.7131138363896385</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106801410929087</v>
+        <v>0.7106827753379817</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107084972209539</v>
+        <v>0.7107114579297953</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.708561737395618</v>
+        <v>0.7085663687817751</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060964167472537</v>
+        <v>0.7061053316497197</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042588937828509</v>
+        <v>0.7042691591456061</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033774475652279</v>
+        <v>0.7033866718944437</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028116779501081</v>
+        <v>0.7028183217976292</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032452833218559</v>
+        <v>0.7032469438946576</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7048958917229783</v>
+        <v>0.7048909261174883</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7063886078358252</v>
+        <v>0.7063732855196501</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7085567078901058</v>
+        <v>0.7085331667299808</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7103018787365961</v>
+        <v>0.7102745218422984</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7102898421763288</v>
+        <v>0.7102586105661645</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7091207604950014</v>
+        <v>0.7090954753911348</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7083119828193873</v>
+        <v>0.7079373877527009</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7087432072471713</v>
+        <v>0.7082936069065637</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7100872029130363</v>
+        <v>0.7095585332677543</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7131336393572942</v>
+        <v>0.7124335079817219</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7158256747533484</v>
+        <v>0.7149691142480908</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7175388440928139</v>
+        <v>0.7165204351978252</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7175572378340175</v>
+        <v>0.7163360866257009</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7167530877766219</v>
+        <v>0.7152825976376179</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7155288091812495</v>
+        <v>0.7137465718059807</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7067064600339535</v>
+        <v>0.7046876690311266</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6974814867950595</v>
+        <v>0.6951356515084262</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6842005154363927</v>
+        <v>0.6815833914996652</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6701341139244907</v>
+        <v>0.6670938347303065</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6593209889244909</v>
+        <v>0.6468912315551816</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505959580471182</v>
+        <v>0.6505954037192365</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514062944159147</v>
+        <v>0.6514060006368573</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524618893159676</v>
+        <v>0.6524613885313693</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497238060070384</v>
+        <v>0.6497235927508124</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464230954980446</v>
+        <v>0.6464228663709609</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431321816505078</v>
+        <v>0.6431319294567875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408147603807716</v>
+        <v>0.6408144934884252</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397993708988536</v>
+        <v>0.6397991037478958</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423540090732363</v>
+        <v>0.642352765743227</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432448291127074</v>
+        <v>0.6432440882863067</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413379057634438</v>
+        <v>0.6413371694534222</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384606880123218</v>
+        <v>0.6384599421456567</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403016547607244</v>
+        <v>0.6402994595824206</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403788333858853</v>
+        <v>0.6403767071182614</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398886106333241</v>
+        <v>0.6398875068497952</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422667560349113</v>
+        <v>0.6422658731852868</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449949230527698</v>
+        <v>0.644993211098225</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468785935018484</v>
+        <v>0.6468763184929374</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465275024877959</v>
+        <v>0.6465255721740922</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467637224537756</v>
+        <v>0.646762611832803</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455325232370936</v>
+        <v>0.6455306578304671</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449691687495223</v>
+        <v>0.6449659406100261</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457294209032323</v>
+        <v>0.645723870495817</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434718457867006</v>
+        <v>0.6434645873054844</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425875265878411</v>
+        <v>0.6425782894050215</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437062409757851</v>
+        <v>0.6436956191433277</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442751283199529</v>
+        <v>0.6442638771508148</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460334055120414</v>
+        <v>0.6460202990261329</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527854585489661</v>
+        <v>0.6527744968662099</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6646079882431276</v>
+        <v>0.6645924158970395</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6718492130544327</v>
+        <v>0.6718317800739497</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6877799533598872</v>
+        <v>0.6877640313715833</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6969907602724287</v>
+        <v>0.696978756407194</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993456873392159</v>
+        <v>0.6993330841161866</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996169159071171</v>
+        <v>0.6996040201523084</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079502724278092</v>
+        <v>0.7079464406741418</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080006353252685</v>
+        <v>0.7079976250192813</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109365144526305</v>
+        <v>0.7109382115376626</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175760329830779</v>
+        <v>0.7175874235856615</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177756885399948</v>
+        <v>0.7177878367163437</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7249854204437395</v>
+        <v>0.7250022974954162</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200839332120619</v>
+        <v>0.7200910838268348</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234724973846745</v>
+        <v>0.7234806791619435</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229582452239509</v>
+        <v>0.7229652813592485</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200822342618671</v>
+        <v>0.7200879571710437</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147402536595063</v>
+        <v>0.714740335340506</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166508570974626</v>
+        <v>0.7166518819426664</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166720709165593</v>
+        <v>0.7166744970951131</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153860184335882</v>
+        <v>0.7153886713946549</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131138363896385</v>
+        <v>0.7131155633467636</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106827753379817</v>
+        <v>0.7106853603202846</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107114579297953</v>
+        <v>0.71071436337079</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085663687817751</v>
+        <v>0.7085709153308553</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7061053316497197</v>
+        <v>0.7061140928664759</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042691591456061</v>
+        <v>0.7042792537409744</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033866718944437</v>
+        <v>0.7033957485621046</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028183217976292</v>
+        <v>0.7028248697140966</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032469438946576</v>
+        <v>0.7032485991243769</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7048909261174883</v>
+        <v>0.7048860718104084</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7063732855196501</v>
+        <v>0.7063582411445954</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7085331667299808</v>
+        <v>0.708510024006789</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7102745218422984</v>
+        <v>0.7102476095290166</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7102586105661645</v>
+        <v>0.7102278484046062</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7090954753911348</v>
+        <v>0.709070514341633</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7079373877527009</v>
+        <v>0.7075781372616983</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7082936069065637</v>
+        <v>0.707862136440277</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7095585332677543</v>
+        <v>0.7090498564997602</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7124335079817219</v>
+        <v>0.7117619837145872</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7149691142480908</v>
+        <v>0.7141501420436385</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7165204351978252</v>
+        <v>0.7155491498749929</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7163360866257009</v>
+        <v>0.7151765878397822</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7152825976376179</v>
+        <v>0.7138946172421758</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7137465718059807</v>
+        <v>0.7120783231632435</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7046876690311266</v>
+        <v>0.7028216655345365</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6951356515084262</v>
+        <v>0.6930205830035987</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6815833914996652</v>
+        <v>0.6793207904936494</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6670938347303065</v>
+        <v>0.6646653671621665</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6468912315551816</v>
+        <v>0.6446159549885988</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505954037192365</v>
+        <v>0.6505948589480153</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514060006368573</v>
+        <v>0.6514057118689537</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524613885313693</v>
+        <v>0.6524608963444845</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497235927508124</v>
+        <v>0.649723383063802</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464228663709609</v>
+        <v>0.6464226410912081</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431319294567875</v>
+        <v>0.6431316815099404</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408144934884252</v>
+        <v>0.6408142310981719</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397991037478958</v>
+        <v>0.6397988411075952</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.642352765743227</v>
+        <v>0.6423515439357186</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432440882863067</v>
+        <v>0.6432433603708356</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413371694534222</v>
+        <v>0.6413364459681782</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384599421456567</v>
+        <v>0.6384592092641908</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6402994595824206</v>
+        <v>0.6402973025485169</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403767071182614</v>
+        <v>0.6403746175787537</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398875068497952</v>
+        <v>0.639886421990673</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422658731852868</v>
+        <v>0.6422650058268761</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.644993211098225</v>
+        <v>0.6449915289268119</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468763184929374</v>
+        <v>0.6468740825631829</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465255721740922</v>
+        <v>0.6465236748331191</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646762611832803</v>
+        <v>0.6467615202512369</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455306578304671</v>
+        <v>0.6455288244959529</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449659406100261</v>
+        <v>0.644962768310916</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.645723870495817</v>
+        <v>0.6457184154785393</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434645873054844</v>
+        <v>0.6434574533957733</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425782894050215</v>
+        <v>0.6425692107698187</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6436956191433277</v>
+        <v>0.6436851791971058</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442638771508148</v>
+        <v>0.6442528181960397</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460202990261329</v>
+        <v>0.6460074166625664</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527744968662099</v>
+        <v>0.6527637243321598</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6645924158970395</v>
+        <v>0.6645771110418055</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6718317800739497</v>
+        <v>0.6718146467636008</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6877640313715833</v>
+        <v>0.6877483792430786</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.696978756407194</v>
+        <v>0.6969669554572964</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993330841161866</v>
+        <v>0.6993206927129303</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996040201523084</v>
+        <v>0.6995913390772293</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079464406741418</v>
+        <v>0.707942669262409</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7079976250192813</v>
+        <v>0.7079946603024236</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109382115376626</v>
+        <v>0.7109398734329087</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175874235856615</v>
+        <v>0.7175986181423526</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177878367163437</v>
+        <v>0.7177997772623128</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7250022974954162</v>
+        <v>0.725018889367284</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200910838268348</v>
+        <v>0.7200981130819624</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234806791619435</v>
+        <v>0.7234887226153135</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229652813592485</v>
+        <v>0.7229722001934158</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200879571710437</v>
+        <v>0.7200935859648294</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714740335340506</v>
+        <v>0.7147404161594924</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166518819426664</v>
+        <v>0.7166528909616222</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166744970951131</v>
+        <v>0.7166768829657053</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153886713946549</v>
+        <v>0.7153912793195429</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131155633467636</v>
+        <v>0.7131172592680716</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106853603202846</v>
+        <v>0.7106878974012163</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.71071436337079</v>
+        <v>0.7107172150685661</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085709153308553</v>
+        <v>0.7085753793417825</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7061140928664759</v>
+        <v>0.706122704323316</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042792537409744</v>
+        <v>0.7042891817687958</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033957485621046</v>
+        <v>0.7034046810454446</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028248697140966</v>
+        <v>0.7028313236792251</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032485991243769</v>
+        <v>0.7032502485814629</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7048860718104084</v>
+        <v>0.7048813253690982</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7063582411445954</v>
+        <v>0.7063434673757719</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.708510024006789</v>
+        <v>0.7084872699028947</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7102476095290166</v>
+        <v>0.7102211313597793</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7102278484046062</v>
+        <v>0.7101975456750071</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.709070514341633</v>
+        <v>0.7090458719887422</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7075781372616983</v>
+        <v>0.707274993858055</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.707862136440277</v>
+        <v>0.7074960999234039</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7090498564997602</v>
+        <v>0.7086181014814142</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7117619837145872</v>
+        <v>0.7111813379435004</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7141501420436385</v>
+        <v>0.7134368394775781</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7155491498749929</v>
+        <v>0.7146979082092254</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7151765878397822</v>
+        <v>0.7141586508143885</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7138946172421758</v>
+        <v>0.7126767370945977</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7120783231632435</v>
+        <v>0.7106202937189614</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7028216655345365</v>
+        <v>0.7012171365293</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6930205830035987</v>
+        <v>0.6912595952449867</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6793207904936494</v>
+        <v>0.6775480755144796</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6646653671621665</v>
+        <v>0.6629631332031936</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6446159549885988</v>
+        <v>0.6438450796087118</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505948589480153</v>
+        <v>0.6505943234884368</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514057118689537</v>
+        <v>0.6514054279850917</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524608963444845</v>
+        <v>0.6524604125357969</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649723383063802</v>
+        <v>0.6497231768572314</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464226410912081</v>
+        <v>0.6464224195627658</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431316815099404</v>
+        <v>0.6431314377036563</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408142310981719</v>
+        <v>0.640813973097113</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397988411075952</v>
+        <v>0.6397985828647305</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423515439357186</v>
+        <v>0.6423503430967328</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432433603708356</v>
+        <v>0.6432426450317705</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413364459681782</v>
+        <v>0.6413357349756084</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384592092641908</v>
+        <v>0.6384584890318181</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6402973025485169</v>
+        <v>0.6402951826735842</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403746175787537</v>
+        <v>0.6403725638241746</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.639886421990673</v>
+        <v>0.6398853555734949</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422650058268761</v>
+        <v>0.6422641535556642</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449915289268119</v>
+        <v>0.6449898757683326</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468740825631829</v>
+        <v>0.6468718847147625</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465236748331191</v>
+        <v>0.6465218096275965</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467615202512369</v>
+        <v>0.6467604472238874</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455288244959529</v>
+        <v>0.6455270224138721</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.644962768310916</v>
+        <v>0.6449596504164143</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457184154785393</v>
+        <v>0.6457130534141634</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434574533957733</v>
+        <v>0.6434504408797227</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425692107698187</v>
+        <v>0.6425602866376958</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6436851791971058</v>
+        <v>0.6436749165087655</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442528181960397</v>
+        <v>0.6442419465765978</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460074166625664</v>
+        <v>0.6459947527277726</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527637243321598</v>
+        <v>0.6527531360972985</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6645771110418055</v>
+        <v>0.6645620668511932</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6718146467636008</v>
+        <v>0.6717978054705429</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6877483792430786</v>
+        <v>0.6877329901798059</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6969669554572964</v>
+        <v>0.696955352328136</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993206927129303</v>
+        <v>0.6993085078436445</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6995913390772293</v>
+        <v>0.6995788673790196</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.707942669262409</v>
+        <v>0.7079389567911361</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7079946603024236</v>
+        <v>0.7079917401653738</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109398734329087</v>
+        <v>0.7109415011875257</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175986181423526</v>
+        <v>0.7176096216658157</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177997772623128</v>
+        <v>0.7178115154484817</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.725018889367284</v>
+        <v>0.7250352032192201</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200981130819624</v>
+        <v>0.7201050240366408</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234887226153135</v>
+        <v>0.7234966312171212</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229722001934158</v>
+        <v>0.7229790046285757</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200935859648294</v>
+        <v>0.7200991229390215</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147404161594924</v>
+        <v>0.7147404961247948</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166528909616222</v>
+        <v>0.7166538845138141</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166768829657053</v>
+        <v>0.7166792295234538</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153912793195429</v>
+        <v>0.7153938433457695</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131172592680716</v>
+        <v>0.7131189249819461</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106878974012163</v>
+        <v>0.710690387892714</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107172150685661</v>
+        <v>0.7107200144924573</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085753793417825</v>
+        <v>0.7085797630315116</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.706122704323316</v>
+        <v>0.7061311698139381</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042891817687958</v>
+        <v>0.7042989472932106</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7034046810454446</v>
+        <v>0.7034134727147967</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028313236792251</v>
+        <v>0.7028376856218319</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032502485814629</v>
+        <v>0.7032518918689044</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7048813253690982</v>
+        <v>0.704876683494026</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7063434673757719</v>
+        <v>0.7063289571291841</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7084872699028947</v>
+        <v>0.7084648949135357</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7102211313597793</v>
+        <v>0.7101950772110418</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7101975456750071</v>
+        <v>0.7101676926257157</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7090458719887422</v>
+        <v>0.7090215430567487</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.707274993858055</v>
+        <v>0.7069839745143214</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7074960999234039</v>
+        <v>0.7071440734741093</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7086181014814142</v>
+        <v>0.7082017666463929</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7111813379435004</v>
+        <v>0.710624354753935</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7134368394775781</v>
+        <v>0.712754041154944</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7146979082092254</v>
+        <v>0.7138849922754633</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7141586508143885</v>
+        <v>0.7131904889892753</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7126767370945977</v>
+        <v>0.7115246068818208</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7106202937189614</v>
+        <v>0.7092511903188166</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7012171365293</v>
+        <v>0.6997270626326375</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6912595952449867</v>
+        <v>0.6896582164465037</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6775480755144796</v>
+        <v>0.6759889653604065</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6629631332031936</v>
+        <v>0.6615483021030598</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6438450796087118</v>
+        <v>0.6433332822893052</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B119"/>
+  <dimension ref="A1:B120"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505943234884368</v>
+        <v>0.650593797103787</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514054279850917</v>
+        <v>0.6514051488624218</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524604125357969</v>
+        <v>0.6524599368931996</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497231768572314</v>
+        <v>0.6497229740452413</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464224195627658</v>
+        <v>0.6464222016927802</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431314377036563</v>
+        <v>0.6431311979351411</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640813973097113</v>
+        <v>0.6408137193760904</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397985828647305</v>
+        <v>0.6397983289098352</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423503430967328</v>
+        <v>0.6423491626911401</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432426450317705</v>
+        <v>0.6432419419460427</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413357349756084</v>
+        <v>0.641335036154975</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384584890318181</v>
+        <v>0.6384577811239304</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6402951826735842</v>
+        <v>0.6402930990058401</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403725638241746</v>
+        <v>0.6403705449433472</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398853555734949</v>
+        <v>0.6398843071320565</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422641535556642</v>
+        <v>0.6422633159815587</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449898757683326</v>
+        <v>0.6449882508789078</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468718847147625</v>
+        <v>0.6468697239835202</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465218096275965</v>
+        <v>0.6465199757483419</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467604472238874</v>
+        <v>0.6467593922819044</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455270224138721</v>
+        <v>0.6455252507922284</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449596504164143</v>
+        <v>0.6449565855395248</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457130534141634</v>
+        <v>0.6457077819477528</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434504408797227</v>
+        <v>0.6434435466866076</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425602866376958</v>
+        <v>0.6425515131004335</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6436749165087655</v>
+        <v>0.6436648266055371</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442419465765978</v>
+        <v>0.6442312575770374</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6459947527277726</v>
+        <v>0.6459823017191976</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527531360972985</v>
+        <v>0.6527427274763382</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6645620668511932</v>
+        <v>0.6645472767290395</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6717978054705429</v>
+        <v>0.6717812488000384</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6877329901798059</v>
+        <v>0.6877178576131129</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.696955352328136</v>
+        <v>0.6969439420939931</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993085078436445</v>
+        <v>0.6992965243966189</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6995788673790196</v>
+        <v>0.699566599927576</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079389567911361</v>
+        <v>0.707935301901454</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7079917401653738</v>
+        <v>0.7079888636276969</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109415011875257</v>
+        <v>0.7109430958103063</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7176096216658157</v>
+        <v>0.7176204389994483</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7178115154484817</v>
+        <v>0.7178230563687855</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7250352032192201</v>
+        <v>0.7250512459736733</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7201050240366408</v>
+        <v>0.7201118196482507</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234966312171212</v>
+        <v>0.7235044083246531</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229790046285757</v>
+        <v>0.7229856974721389</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200991229390215</v>
+        <v>0.7201045703155864</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147404961247948</v>
+        <v>0.7147405752449181</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166538845138141</v>
+        <v>0.7166548629480759</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166792295234538</v>
+        <v>0.7166815377310222</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153938433457695</v>
+        <v>0.7153963645728489</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131189249819461</v>
+        <v>0.7131205612875798</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710690387892714</v>
+        <v>0.7106928330594696</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107200144924573</v>
+        <v>0.7107227630589745</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085797630315116</v>
+        <v>0.7085840685386355</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7061311698139381</v>
+        <v>0.7061394930054332</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7042989472932106</v>
+        <v>0.7043085542480566</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7034134727147967</v>
+        <v>0.7034221268376057</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028376856218319</v>
+        <v>0.7028439574213043</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032518918689044</v>
+        <v>0.7032535286201665</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.704876683494026</v>
+        <v>0.704872143012597</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7063289571291841</v>
+        <v>0.7063147035612888</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7084648949135357</v>
+        <v>0.7084428898347543</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7101950772110418</v>
+        <v>0.7101694372614767</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7101676926257157</v>
+        <v>0.7101382797622258</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7090215430567487</v>
+        <v>0.7089975223525685</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7069839745143214</v>
+        <v>0.7069688389367785</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7071440734741093</v>
+        <v>0.7069185061620478</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7082017666463929</v>
+        <v>0.7079331704144304</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.710624354753935</v>
+        <v>0.7102617620684433</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.712754041154944</v>
+        <v>0.7122277814422735</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7138849922754633</v>
+        <v>0.7132827108936719</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7131904889892753</v>
+        <v>0.7124987559720379</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7115246068818208</v>
+        <v>0.7107326379000545</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7092511903188166</v>
+        <v>0.7083517288927241</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.6997270626326375</v>
+        <v>0.6989631075515941</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6896582164465037</v>
+        <v>0.6889669297127334</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6759889653604065</v>
+        <v>0.6756915201941175</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6615483021030598</v>
+        <v>0.6618941732853711</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,15 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6433332822893052</v>
+        <v>0.6457928757893817</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
+        <v>46395</v>
+      </c>
+      <c r="B120">
+        <v>0.6544928757893818</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7079331704144304</v>
+        <v>0.7079343477845896</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7102617620684433</v>
+        <v>0.7102618945607299</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7122277814422735</v>
+        <v>0.7122636462469084</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7132827108936719</v>
+        <v>0.7133100693462701</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7124987559720379</v>
+        <v>0.7125185068033126</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7107326379000545</v>
+        <v>0.7107468576631248</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7083517288927241</v>
+        <v>0.7083617720323225</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.6989631075515941</v>
+        <v>0.6989698594853009</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6889669297127334</v>
+        <v>0.6889724797763656</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6756915201941175</v>
+        <v>0.6756947187617446</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6618941732853711</v>
+        <v>0.6618955937108646</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6457928757893817</v>
+        <v>0.6457925817577022</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.6544928757893818</v>
+        <v>0.6544925817577022</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650593797103787</v>
+        <v>0.6505932795653078</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514051488624218</v>
+        <v>0.6514048743821791</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524599368931996</v>
+        <v>0.6524594692116847</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497229740452413</v>
+        <v>0.649722774544771</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464222016927802</v>
+        <v>0.6464219873914347</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431311979351411</v>
+        <v>0.6431309621049739</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408137193760904</v>
+        <v>0.640813469829535</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397983289098352</v>
+        <v>0.6397980791370453</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423491626911401</v>
+        <v>0.6423480022018642</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432419419460427</v>
+        <v>0.6432412508015537</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.641335036154975</v>
+        <v>0.6413343491964247</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384577811239304</v>
+        <v>0.6384570852269307</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6402930990058401</v>
+        <v>0.6402910506257248</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403705449433472</v>
+        <v>0.6403685600557598</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398843071320565</v>
+        <v>0.6398832762157337</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422633159815587</v>
+        <v>0.6422624927277948</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449882508789078</v>
+        <v>0.6449866535398636</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468697239835202</v>
+        <v>0.6468675994375577</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465199757483419</v>
+        <v>0.6465181724131004</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467593922819044</v>
+        <v>0.6467583549720934</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455252507922284</v>
+        <v>0.6455235088655504</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449565855395248</v>
+        <v>0.6449535723399803</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457077819477528</v>
+        <v>0.645702598803225</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434435466866076</v>
+        <v>0.6434367678483501</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425515131004335</v>
+        <v>0.6425428863804381</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6436648266055371</v>
+        <v>0.6436549051637568</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442312575770374</v>
+        <v>0.6442207466386918</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6459823017191976</v>
+        <v>0.6459700583173684</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527427274763382</v>
+        <v>0.6527324939413341</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6645472767290395</v>
+        <v>0.6645327342996482</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6717812488000384</v>
+        <v>0.671764969604677</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6877178576131129</v>
+        <v>0.6877029751909615</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6969439420939931</v>
+        <v>0.6969327199910986</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6992965243966189</v>
+        <v>0.6992847374271384</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.699566599927576</v>
+        <v>0.6995545317585938</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.707935301901454</v>
+        <v>0.7079317032755155</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7079888636276969</v>
+        <v>0.7079860297368497</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109430958103063</v>
+        <v>0.7109446582715686</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7176204389994483</v>
+        <v>0.7176310748244601</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7178230563687855</v>
+        <v>0.7178344049478442</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7250512459736733</v>
+        <v>0.7250670243254138</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7201118196482507</v>
+        <v>0.7201185027765507</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7235044083246531</v>
+        <v>0.7235120571848612</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229856974721389</v>
+        <v>0.7229922814406248</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7201045703155864</v>
+        <v>0.7201099302455939</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147405752449181</v>
+        <v>0.7147406535285157</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166548629480759</v>
+        <v>0.7166558266029763</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166815377310222</v>
+        <v>0.7166838085199316</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153963645728489</v>
+        <v>0.7153988440638687</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131205612875798</v>
+        <v>0.7131221689562477</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106928330594696</v>
+        <v>0.710695234121029</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107227630589745</v>
+        <v>0.7107254621341498</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085840685386355</v>
+        <v>0.7085882979268032</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7061394930054332</v>
+        <v>0.7061476774435055</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7043085542480566</v>
+        <v>0.7043180064420144</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7034221268376057</v>
+        <v>0.7034306465822664</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028439574213043</v>
+        <v>0.702850140909024</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032535286201665</v>
+        <v>0.7032551584972613</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.704872143012597</v>
+        <v>0.7048677008733152</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7063147035612888</v>
+        <v>0.7063007000590611</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7084428898347543</v>
+        <v>0.7084212457518659</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7101694372614767</v>
+        <v>0.7101442019812165</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7101382797622258</v>
+        <v>0.7101092978395512</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7089975223525685</v>
+        <v>0.7089738047661184</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7069688389367785</v>
+        <v>0.7069538281228851</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7069185061620478</v>
+        <v>0.7066049180389171</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7079343477845896</v>
+        <v>0.7075626838879016</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7102618945607299</v>
+        <v>0.7097680308273793</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7122636462469084</v>
+        <v>0.7116331329498932</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7133100693462701</v>
+        <v>0.7125724185605089</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7125185068033126</v>
+        <v>0.7116597132172344</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7107468576631248</v>
+        <v>0.7097523276777742</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7083617720323225</v>
+        <v>0.7072171338999538</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.6989698594853009</v>
+        <v>0.6978900974808875</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6889724797763656</v>
+        <v>0.6878320376204216</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6756947187617446</v>
+        <v>0.6747497216530881</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6618955937108646</v>
+        <v>0.6612531662914694</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6457925817577022</v>
+        <v>0.6459878352309676</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.6544925817577022</v>
+        <v>0.6480467570806949</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505932795653078</v>
+        <v>0.650598276137422</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514048743821791</v>
+        <v>0.6514075223458328</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524594692116847</v>
+        <v>0.6524639830999285</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.649722774544771</v>
+        <v>0.6497246966088902</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464219873914347</v>
+        <v>0.6464240525187235</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431309621049739</v>
+        <v>0.6431332351521228</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640813469829535</v>
+        <v>0.6408158753693041</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397980791370453</v>
+        <v>0.6398004870144826</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423480022018642</v>
+        <v>0.6423592094056797</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432412508015537</v>
+        <v>0.6432479286484873</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413343491964247</v>
+        <v>0.6413409863204292</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384570852269307</v>
+        <v>0.6384638084850808</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6402910506257248</v>
+        <v>0.6403108378904248</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403685600557598</v>
+        <v>0.6403877258032399</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398832762157337</v>
+        <v>0.6398932252709426</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422624927277948</v>
+        <v>0.6422704509491814</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449866535398636</v>
+        <v>0.6450020850949597</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468675994375577</v>
+        <v>0.6468881055490218</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465181724131004</v>
+        <v>0.6465355712696003</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467583549720934</v>
+        <v>0.6467683656486553</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455235088655504</v>
+        <v>0.6455403230173329</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449535723399803</v>
+        <v>0.6449826702586756</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.645702598803225</v>
+        <v>0.6457526282679167</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434367678483501</v>
+        <v>0.6435021930035666</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425428863804381</v>
+        <v>0.6426261468017119</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6436549051637568</v>
+        <v>0.6437506455725545</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442207466386918</v>
+        <v>0.6443221588569408</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6459700583173684</v>
+        <v>0.6460881937162539</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527324939413341</v>
+        <v>0.6528312999226344</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6645327342996482</v>
+        <v>0.6646730976943911</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.671764969604677</v>
+        <v>0.6719221044209024</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6877029751909615</v>
+        <v>0.6878464842718793</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6969327199910986</v>
+        <v>0.6970409131084843</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6992847374271384</v>
+        <v>0.6993983306669711</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6995545317585938</v>
+        <v>0.6996707582473805</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079317032755155</v>
+        <v>0.7079662324776475</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7079860297368497</v>
+        <v>0.7080131536970485</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109446582715686</v>
+        <v>0.7109293517033211</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7176310748244601</v>
+        <v>0.7175284035076452</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7178344049478442</v>
+        <v>0.7177249074931891</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7250670243254138</v>
+        <v>0.7249149083419177</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7201185027765507</v>
+        <v>0.7200540521553181</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7235120571848612</v>
+        <v>0.7234383132779136</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229922814406248</v>
+        <v>0.7229288660832547</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7201099302455939</v>
+        <v>0.720058352794317</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147406535285157</v>
+        <v>0.7147399181566074</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166558266029763</v>
+        <v>0.7166465918687456</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166838085199316</v>
+        <v>0.7166619420053317</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153988440638687</v>
+        <v>0.7153749320518419</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131221689562477</v>
+        <v>0.7131066005362103</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.710695234121029</v>
+        <v>0.7106719283750378</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107254621341498</v>
+        <v>0.7106992673556987</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085882979268032</v>
+        <v>0.7085473099144306</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7061476774435055</v>
+        <v>0.706068708562767</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7043180064420144</v>
+        <v>0.7048053671776089</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7034306465822664</v>
+        <v>0.7033609591489871</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.702850140909024</v>
+        <v>0.7027778021969855</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032551584972613</v>
+        <v>0.7027840709449101</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7048677008733152</v>
+        <v>0.7042453739765437</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7063007000590611</v>
+        <v>0.7053850194213147</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7084212457518659</v>
+        <v>0.7067932179091585</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7101442019812165</v>
+        <v>0.7087840454174075</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7101092978395512</v>
+        <v>0.708801095330987</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7089738047661184</v>
+        <v>0.7078852173731671</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7069538281228851</v>
+        <v>0.7059720150179574</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7066049180389171</v>
+        <v>0.7044588092883886</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7075626838879016</v>
+        <v>0.7054911294050974</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7097680308273793</v>
+        <v>0.7084047957401939</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7116331329498932</v>
+        <v>0.710178735192768</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7125724185605089</v>
+        <v>0.7120745602217855</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7116597132172344</v>
+        <v>0.7117783627955778</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7097523276777742</v>
+        <v>0.7096001439709435</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7072171338999538</v>
+        <v>0.707032848926098</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.6978900974808875</v>
+        <v>0.70296012812358</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6878320376204216</v>
+        <v>0.6981719621865106</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6747497216530881</v>
+        <v>0.6887193453310594</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6612531662914694</v>
+        <v>0.6784781382636793</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6459878352309676</v>
+        <v>0.6677381960753768</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.6480467570806949</v>
+        <v>0.670424588267753</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.650598276137422</v>
+        <v>0.6505922701496372</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514075223458328</v>
+        <v>0.6514043388933398</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524639830999285</v>
+        <v>0.6524585569456164</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497246966088902</v>
+        <v>0.6497223851594659</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464240525187235</v>
+        <v>0.6464215691498494</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431332351521228</v>
+        <v>0.6431305018780448</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408158753693041</v>
+        <v>0.6408129828546159</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398004870144826</v>
+        <v>0.6397975917314564</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423592094056797</v>
+        <v>0.6423457389897314</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432479286484873</v>
+        <v>0.6432399031399952</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413409863204292</v>
+        <v>0.641333009677857</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384638084850808</v>
+        <v>0.6384557282635057</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403108378904248</v>
+        <v>0.6402870562032097</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403877258032399</v>
+        <v>0.6403646888839724</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398932252709426</v>
+        <v>0.6398812652299968</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422704509491814</v>
+        <v>0.6422608877375169</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6450020850949597</v>
+        <v>0.6449835387579508</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468881055490218</v>
+        <v>0.6468634553272169</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465355712696003</v>
+        <v>0.6465146543736728</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467683656486553</v>
+        <v>0.6467563315106456</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455403230173329</v>
+        <v>0.6455201111612736</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449826702586756</v>
+        <v>0.6449476958338881</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457526282679167</v>
+        <v>0.6456924887502904</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6435021930035666</v>
+        <v>0.6434235448520292</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426261468017119</v>
+        <v>0.6425260589028161</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437506455725545</v>
+        <v>0.6436355510787708</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6443221588569408</v>
+        <v>0.6442002414564909</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460881937162539</v>
+        <v>0.6459461739265691</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528312999226344</v>
+        <v>0.6527125347651833</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6646730976943911</v>
+        <v>0.6645043680644023</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6719221044209024</v>
+        <v>0.6717332162254177</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6878464842718793</v>
+        <v>0.6876739364025659</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970409131084843</v>
+        <v>0.6969108218944966</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993983306669711</v>
+        <v>0.6992617339367486</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996707582473805</v>
+        <v>0.6995309742003482</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079662324776475</v>
+        <v>0.7079246697395423</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080131536970485</v>
+        <v>0.7079804862192429</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109293517033211</v>
+        <v>0.7109476904090606</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175284035076452</v>
+        <v>0.7176518199025335</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177249074931891</v>
+        <v>0.7178565439755886</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7249149083419177</v>
+        <v>0.7250978135166427</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200540521553181</v>
+        <v>0.7201315425578884</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234383132779136</v>
+        <v>0.7235269826261573</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229288660832547</v>
+        <v>0.7230051331856526</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.720058352794317</v>
+        <v>0.7201203960323783</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147399181566074</v>
+        <v>0.7147408076213548</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166465918687456</v>
+        <v>0.7166577108798323</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166619420053317</v>
+        <v>0.7166882414195707</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153749320518419</v>
+        <v>0.7154036819168451</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131066005362103</v>
+        <v>0.7131253013353755</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106719283750378</v>
+        <v>0.7106999085928336</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7106992673556987</v>
+        <v>0.710730717035405</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085473099144306</v>
+        <v>0.7085965362454379</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.706068708562767</v>
+        <v>0.7061636436647984</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7048053671776089</v>
+        <v>0.7043364611854017</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033609591489871</v>
+        <v>0.7034472951373263</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027778021969855</v>
+        <v>0.7028622500429791</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7027840709449101</v>
+        <v>0.7032583964090232</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7042453739765437</v>
+        <v>0.7048590999878164</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7053850194213147</v>
+        <v>0.7062734178958237</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7067932179091585</v>
+        <v>0.7083790062957742</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7087840454174075</v>
+        <v>0.7100949087049149</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.708801095330987</v>
+        <v>0.7100525910401092</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7078852173731671</v>
+        <v>0.7089272589219586</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7059720150179574</v>
+        <v>0.7069241806026592</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7044588092883886</v>
+        <v>0.7062025699561816</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7054911294050974</v>
+        <v>0.7070913061242279</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7084047957401939</v>
+        <v>0.7091273460804511</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.710178735192768</v>
+        <v>0.7107652726554984</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7120745602217855</v>
+        <v>0.7115667868249186</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7117783627955778</v>
+        <v>0.7104969673823343</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7096001439709435</v>
+        <v>0.7084272700056388</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.707032848926098</v>
+        <v>0.7057335351846943</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.70296012812358</v>
+        <v>0.6966830400941286</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6981719621865106</v>
+        <v>0.6868393484077573</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6887193453310594</v>
+        <v>0.6744785376654188</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6784781382636793</v>
+        <v>0.6620127879420543</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6677381960753768</v>
+        <v>0.6491690720097559</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.670424588267753</v>
+        <v>0.6520696369914601</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505922701496372</v>
+        <v>0.6505976809533377</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514043388933398</v>
+        <v>0.6514072071590534</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524585569456164</v>
+        <v>0.652463445569327</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497223851594659</v>
+        <v>0.6497244681251938</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464215691498494</v>
+        <v>0.6464238069738797</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431305018780448</v>
+        <v>0.6431329648319994</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408129828546159</v>
+        <v>0.640815589258932</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397975917314564</v>
+        <v>0.6398002006076964</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423457389897314</v>
+        <v>0.6423578740386647</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432399031399952</v>
+        <v>0.6432471325855048</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.641333009677857</v>
+        <v>0.6413401951445677</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384557282635057</v>
+        <v>0.6384630070680256</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6402870562032097</v>
+        <v>0.640308479553083</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403646888839724</v>
+        <v>0.6403854424998046</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398812652299968</v>
+        <v>0.6398920406141442</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422608877375169</v>
+        <v>0.6422695017934485</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449835387579508</v>
+        <v>0.64500024573707</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468634553272169</v>
+        <v>0.6468856635184004</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465146543736728</v>
+        <v>0.6465335000858163</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467563315106456</v>
+        <v>0.6467671736654499</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455201111612736</v>
+        <v>0.6455383205277415</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449476958338881</v>
+        <v>0.6449792033460546</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6456924887502904</v>
+        <v>0.6457466701506149</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434235448520292</v>
+        <v>0.6434944021452891</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425260589028161</v>
+        <v>0.6426162320401908</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6436355510787708</v>
+        <v>0.6437392465535803</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442002414564909</v>
+        <v>0.6443100865102599</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6459461739265691</v>
+        <v>0.6460741296832309</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527125347651833</v>
+        <v>0.6528195296031349</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6645043680644023</v>
+        <v>0.664656382155917</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6717332162254177</v>
+        <v>0.6719033906592538</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6876739364025659</v>
+        <v>0.6878294100270416</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6969108218944966</v>
+        <v>0.6970280429950821</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6992617339367486</v>
+        <v>0.699384823555684</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6995309742003482</v>
+        <v>0.6996569470260396</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079246697395423</v>
+        <v>0.7079621444296513</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7079804862192429</v>
+        <v>0.7080099503265191</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109476904090606</v>
+        <v>0.7109312009189288</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7176518199025335</v>
+        <v>0.7175406320750594</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7178565439755886</v>
+        <v>0.7177379427083831</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7250978135166427</v>
+        <v>0.7249330028305425</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7201315425578884</v>
+        <v>0.7200617209963607</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7235269826261573</v>
+        <v>0.7234470855543353</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7230051331856526</v>
+        <v>0.722936402483547</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7201203960323783</v>
+        <v>0.7200644767107762</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147408076213548</v>
+        <v>0.7147400033643861</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166577108798323</v>
+        <v>0.7166476838412144</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166882414195707</v>
+        <v>0.716664540065716</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7154036819168451</v>
+        <v>0.715377777352702</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131253013353755</v>
+        <v>0.7131084605529033</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106999085928336</v>
+        <v>0.7106747191073659</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.710730717035405</v>
+        <v>0.7107024036089099</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085965362454379</v>
+        <v>0.7085522104834685</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7061636436647984</v>
+        <v>0.7060781094865747</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7043364611854017</v>
+        <v>0.7048160893187896</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7034472951373263</v>
+        <v>0.7033710116928447</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028622500429791</v>
+        <v>0.7027853897854354</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032583964090232</v>
+        <v>0.7027877221546668</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7048590999878164</v>
+        <v>0.7042428223398381</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7062734178958237</v>
+        <v>0.7053719491238583</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7083790062957742</v>
+        <v>0.7067723320318251</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7100949087049149</v>
+        <v>0.7087583155977975</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7100525910401092</v>
+        <v>0.7087709418874358</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7089272589219586</v>
+        <v>0.7078592583377632</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7069241806026592</v>
+        <v>0.7059540487952896</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7062025699561816</v>
+        <v>0.7042643237428867</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7070913061242279</v>
+        <v>0.7052541955191549</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7091273460804511</v>
+        <v>0.7081246649290754</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7107652726554984</v>
+        <v>0.7098194530169212</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7115667868249186</v>
+        <v>0.7116047559334404</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7104969673823343</v>
+        <v>0.7111985615358272</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7084272700056388</v>
+        <v>0.7089432494735501</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7057335351846943</v>
+        <v>0.7063138128719479</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.6966830400941286</v>
+        <v>0.7022508917282493</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6868393484077573</v>
+        <v>0.6975082373462648</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6744785376654188</v>
+        <v>0.6883511450753579</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6620127879420543</v>
+        <v>0.6785124723734386</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6491690720097559</v>
+        <v>0.6685309314299844</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.6520696369914601</v>
+        <v>0.670658822221935</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505976809533377</v>
+        <v>0.6505917778518071</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514072071590534</v>
+        <v>0.6514040776661657</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.652463445569327</v>
+        <v>0.6524581119839654</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497244681251938</v>
+        <v>0.6497221951215107</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464238069738797</v>
+        <v>0.6464213650440824</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431329648319994</v>
+        <v>0.6431302772981017</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640815589258932</v>
+        <v>0.6408127452317713</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6398002006076964</v>
+        <v>0.639797353903649</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423578740386647</v>
+        <v>0.6423446353163799</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432471325855048</v>
+        <v>0.6432392460495344</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413401951445677</v>
+        <v>0.6413323565485473</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384630070680256</v>
+        <v>0.6384550666208884</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.640308479553083</v>
+        <v>0.6402851084709705</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403854424998046</v>
+        <v>0.6403628009808766</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398920406141442</v>
+        <v>0.6398802843315824</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422695017934485</v>
+        <v>0.6422601053091761</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.64500024573707</v>
+        <v>0.6449820199944969</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468856635184004</v>
+        <v>0.6468614340486272</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465335000858163</v>
+        <v>0.6465129382298958</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467671736654499</v>
+        <v>0.646755344525234</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455383205277415</v>
+        <v>0.6455184539757152</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449792033460546</v>
+        <v>0.6449448300633698</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457466701506149</v>
+        <v>0.6456875576553419</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434944021452891</v>
+        <v>0.643417095233817</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426162320401908</v>
+        <v>0.6425178511957698</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437392465535803</v>
+        <v>0.6436261104798477</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6443100865102599</v>
+        <v>0.6441902388226907</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460741296832309</v>
+        <v>0.6459345231479954</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528195296031349</v>
+        <v>0.6527028007975593</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.664656382155917</v>
+        <v>0.6644905325295836</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6719033906592538</v>
+        <v>0.6717177288936318</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6878294100270416</v>
+        <v>0.6876597683378376</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970280429950821</v>
+        <v>0.6969001371252526</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.699384823555684</v>
+        <v>0.6992505083022309</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996569470260396</v>
+        <v>0.69951947565339</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079621444296513</v>
+        <v>0.7079212323855866</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080099503265191</v>
+        <v>0.707977774818451</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109312009189288</v>
+        <v>0.7109491618491509</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175406320750594</v>
+        <v>0.7176619377659602</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177379427083831</v>
+        <v>0.7178673434879561</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7249330028305425</v>
+        <v>0.7251128366885247</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200617209963607</v>
+        <v>0.7201379044772811</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234470855543353</v>
+        <v>0.7235342651887975</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.722936402483547</v>
+        <v>0.7230114059726779</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200644767107762</v>
+        <v>0.7201255058613281</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147400033643861</v>
+        <v>0.7147408834484447</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166476838412144</v>
+        <v>0.7166586321308356</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.716664540065716</v>
+        <v>0.7166904052485656</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.715377777352702</v>
+        <v>0.7154060422359463</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131084605529033</v>
+        <v>0.713126827459354</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106747191073659</v>
+        <v>0.7107021842338195</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107024036089099</v>
+        <v>0.7107332753605553</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085522104834685</v>
+        <v>0.7086005489568454</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060781094865747</v>
+        <v>0.7061714319759722</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7048160893187896</v>
+        <v>0.7043454707694221</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033710116928447</v>
+        <v>0.7034554298215034</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027853897854354</v>
+        <v>0.7028681791242271</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7027877221546668</v>
+        <v>0.703260003894788</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7042428223398381</v>
+        <v>0.7048549356957809</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7053719491238583</v>
+        <v>0.7062601270785065</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7067723320318251</v>
+        <v>0.7083583944428153</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7087583155977975</v>
+        <v>0.7100708330155802</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7087709418874358</v>
+        <v>0.7100248488554357</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7078592583377632</v>
+        <v>0.7089044208598119</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7059540487952896</v>
+        <v>0.7069095435775525</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7042643237428867</v>
+        <v>0.7059919518078648</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7052541955191549</v>
+        <v>0.706846303327035</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7081246649290754</v>
+        <v>0.7087924054572143</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7098194530169212</v>
+        <v>0.7103200049575811</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7116047559334404</v>
+        <v>0.7110485700266629</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7111985615358272</v>
+        <v>0.709897772482643</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7089432494735501</v>
+        <v>0.7077440650512364</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7063138128719479</v>
+        <v>0.7049676149172268</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7022508917282493</v>
+        <v>0.6960320216562182</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6975082373462648</v>
+        <v>0.6862551563187349</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6883511450753579</v>
+        <v>0.6741741516418487</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6785124723734386</v>
+        <v>0.6620742156315247</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6685309314299844</v>
+        <v>0.6499298867172569</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.670658822221935</v>
+        <v>0.6519972035169905</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.706846303327035</v>
+        <v>0.7068481102446469</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7087924054572143</v>
+        <v>0.7087940738572527</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7103200049575811</v>
+        <v>0.7103324263078028</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7110485700266629</v>
+        <v>0.7110500080814643</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.709897772482643</v>
+        <v>0.7098985379179451</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7077440650512364</v>
+        <v>0.707744328140187</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7049676149172268</v>
+        <v>0.7049674450017063</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.6960320216562182</v>
+        <v>0.6960314326279911</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6862551563187349</v>
+        <v>0.6862544917815538</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6741741516418487</v>
+        <v>0.6741731101043497</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6620742156315247</v>
+        <v>0.6620728964545171</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6499298867172569</v>
+        <v>0.6499280568656456</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.6519972035169905</v>
+        <v>0.6519934110295471</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B120"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505917778518071</v>
+        <v>0.6505970963966856</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514040776661657</v>
+        <v>0.6514068975383807</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524581119839654</v>
+        <v>0.6524629175953938</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497221951215107</v>
+        <v>0.6497242435975829</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464213650440824</v>
+        <v>0.6464235656949381</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431302772981017</v>
+        <v>0.6431326992223099</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408127452317713</v>
+        <v>0.640815308143024</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.639797353903649</v>
+        <v>0.6397999192053907</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423446353163799</v>
+        <v>0.6423565626159765</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432392460495344</v>
+        <v>0.6432463508967696</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413323565485473</v>
+        <v>0.6413394182461423</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384550666208884</v>
+        <v>0.6384622201062735</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6402851084709705</v>
+        <v>0.6403061636695576</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403628009808766</v>
+        <v>0.6403832000468694</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398802843315824</v>
+        <v>0.6398908769890754</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422601053091761</v>
+        <v>0.642268569897266</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449820199944969</v>
+        <v>0.6449984395307526</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468614340486272</v>
+        <v>0.6468832649257266</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465129382298958</v>
+        <v>0.6465314655304393</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.646755344525234</v>
+        <v>0.6467660028407365</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455184539757152</v>
+        <v>0.6455363536911933</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449448300633698</v>
+        <v>0.6449757985497803</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6456875576553419</v>
+        <v>0.6457408180708484</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.643417095233817</v>
+        <v>0.6434867497391327</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425178511957698</v>
+        <v>0.6426064934923291</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6436261104798477</v>
+        <v>0.6437280496320043</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6441902388226907</v>
+        <v>0.6442982276785844</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6459345231479954</v>
+        <v>0.6460603146307862</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527028007975593</v>
+        <v>0.6528079696237192</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6644905325295836</v>
+        <v>0.6646399639243196</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6717177288936318</v>
+        <v>0.6718850099963882</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6876597683378376</v>
+        <v>0.6878126352829445</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6969001371252526</v>
+        <v>0.6970153980158158</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6992505083022309</v>
+        <v>0.6993715513033942</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.69951947565339</v>
+        <v>0.6996433735753873</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079212323855866</v>
+        <v>0.7079581227899128</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.707977774818451</v>
+        <v>0.7080067968925913</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109491618491509</v>
+        <v>0.7109330103026357</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7176619377659602</v>
+        <v>0.7175526426981405</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7178673434879561</v>
+        <v>0.7177507472839387</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7251128366885247</v>
+        <v>0.72495078091225</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7201379044772811</v>
+        <v>0.7200692551310037</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7235342651887975</v>
+        <v>0.7234557043638123</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7230114059726779</v>
+        <v>0.7229438089435998</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7201255058613281</v>
+        <v>0.7200704965263613</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147408834484447</v>
+        <v>0.7147400876792017</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166586321308356</v>
+        <v>0.7166487584346972</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166904052485656</v>
+        <v>0.7166670934844912</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7154060422359463</v>
+        <v>0.7153805726528114</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.713126827459354</v>
+        <v>0.7131102859003061</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7107021842338195</v>
+        <v>0.7106774561718638</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107332753605553</v>
+        <v>0.7107054796617283</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7086005489568454</v>
+        <v>0.7085570187876824</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7061714319759722</v>
+        <v>0.7060873440954116</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7043454707694221</v>
+        <v>0.7048266267410954</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7034554298215034</v>
+        <v>0.7033808978928875</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028681791242271</v>
+        <v>0.7027928623244846</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.703260003894788</v>
+        <v>0.7027913325900572</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7048549356957809</v>
+        <v>0.7042403432932814</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7062601270785065</v>
+        <v>0.705359129028438</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7083583944428153</v>
+        <v>0.7067518192871817</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7100708330155802</v>
+        <v>0.7087330298834481</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7100248488554357</v>
+        <v>0.7087412708361349</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7089044208598119</v>
+        <v>0.7078336682414841</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7069095435775525</v>
+        <v>0.7059362802553946</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7059919518078648</v>
+        <v>0.7042563704812392</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7068481102446469</v>
+        <v>0.70506375990419</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7087940738572527</v>
+        <v>0.7078382869024742</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7103324263078028</v>
+        <v>0.7095120750446132</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7110500080814643</v>
+        <v>0.7112298094333065</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7098985379179451</v>
+        <v>0.7106961990490942</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.707744328140187</v>
+        <v>0.7083918803835692</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7049674450017063</v>
+        <v>0.7057244067454754</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.6960314326279911</v>
+        <v>0.7017029024062256</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6862544917815538</v>
+        <v>0.6970662312065119</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6741731101043497</v>
+        <v>0.6882159538211097</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6620728964545171</v>
+        <v>0.6788165443008556</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6499280568656456</v>
+        <v>0.6696085005640644</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,15 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.6519934110295471</v>
+        <v>0.6716763610706857</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>0.6755773812961567</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505970963966856</v>
+        <v>0.6505912935582864</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514068975383807</v>
+        <v>0.6514038206439654</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524629175953938</v>
+        <v>0.6524576742286832</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497242435975829</v>
+        <v>0.6497220080886351</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464235656949381</v>
+        <v>0.6464211641756841</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431326992223099</v>
+        <v>0.6431300562899019</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.640815308143024</v>
+        <v>0.6408125113941745</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397999192053907</v>
+        <v>0.639797119867671</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423565626159765</v>
+        <v>0.6423435496570257</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432463508967696</v>
+        <v>0.6432385997527164</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413394182461423</v>
+        <v>0.6413317141419301</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384622201062735</v>
+        <v>0.6384544158359597</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403061636695576</v>
+        <v>0.6402831926442984</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403832000468694</v>
+        <v>0.6403609438309747</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398908769890754</v>
+        <v>0.6398793192991449</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.642268569897266</v>
+        <v>0.6422593358165314</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449984395307526</v>
+        <v>0.64498052613839</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468832649257266</v>
+        <v>0.6468594455245349</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465314655304393</v>
+        <v>0.6465112497489891</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467660028407365</v>
+        <v>0.6467543735033026</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455363536911933</v>
+        <v>0.6455168236672604</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449757985497803</v>
+        <v>0.6449420110388158</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457408180708484</v>
+        <v>0.6456827065034205</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434867497391327</v>
+        <v>0.6434107500426616</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6426064934923291</v>
+        <v>0.6425097763976053</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437280496320043</v>
+        <v>0.6436168224200669</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442982276785844</v>
+        <v>0.6441803974588127</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460603146307862</v>
+        <v>0.6459230603836376</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6528079696237192</v>
+        <v>0.6526932252513933</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6646399639243196</v>
+        <v>0.6644769212134933</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6718850099963882</v>
+        <v>0.6717024927231348</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6878126352829445</v>
+        <v>0.687645827005045</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6970153980158158</v>
+        <v>0.6968896229245249</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993715513033942</v>
+        <v>0.6992394609060888</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996433735753873</v>
+        <v>0.6995081580617568</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079581227899128</v>
+        <v>0.707917846404815</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080067968925913</v>
+        <v>0.7079751025146949</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109330103026357</v>
+        <v>0.7109506046585545</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175526426981405</v>
+        <v>0.7176718913533635</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177507472839387</v>
+        <v>0.7178779687987487</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.72495078091225</v>
+        <v>0.7251276201388827</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200692551310037</v>
+        <v>0.7201441644531257</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234557043638123</v>
+        <v>0.7235414314751565</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229438089435998</v>
+        <v>0.7230175799120436</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200704965263613</v>
+        <v>0.7201305361930315</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147400876792017</v>
+        <v>0.714740958474668</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166487584346972</v>
+        <v>0.7166595398612348</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166670934844912</v>
+        <v>0.7166925350976431</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153805726528114</v>
+        <v>0.7154083647359196</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131102859003061</v>
+        <v>0.7131283277755209</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106774561718638</v>
+        <v>0.7107044202345716</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107054796617283</v>
+        <v>0.7107357891963916</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085570187876824</v>
+        <v>0.7086044931168695</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7060873440954116</v>
+        <v>0.7061790945984051</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7048266267410954</v>
+        <v>0.7043543396704577</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7033808978928875</v>
+        <v>0.7034634418816627</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7027928623244846</v>
+        <v>0.7028740267663236</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7027913325900572</v>
+        <v>0.7032616034055246</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7042403432932814</v>
+        <v>0.7048508586445903</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.705359129028438</v>
+        <v>0.7062470619975035</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7067518192871817</v>
+        <v>0.7083381106065416</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7087330298834481</v>
+        <v>0.7100471265903163</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7087412708361349</v>
+        <v>0.7099975029820361</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7078336682414841</v>
+        <v>0.708881866306068</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7059362802553946</v>
+        <v>0.7068950306926172</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7042563704812392</v>
+        <v>0.7059857425923083</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.70506375990419</v>
+        <v>0.7066439034775758</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7078382869024742</v>
+        <v>0.7085343927947859</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7095120750446132</v>
+        <v>0.7100253750379988</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7112298094333065</v>
+        <v>0.7106243569671464</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7106961990490942</v>
+        <v>0.7094075285981309</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7083918803835692</v>
+        <v>0.7071955045340976</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7057244067454754</v>
+        <v>0.7043848071472076</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.7017029024062256</v>
+        <v>0.6956248743097835</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6970662312065119</v>
+        <v>0.6861013551756628</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6882159538211097</v>
+        <v>0.6743501546457293</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6788165443008556</v>
+        <v>0.6627533723632648</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6696085005640644</v>
+        <v>0.6515452583699267</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.6716763610706857</v>
+        <v>0.6539734323474868</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>0.6755773812961567</v>
+        <v>0.6608633942858556</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505912935582864</v>
+        <v>0.6505965221853514</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514038206439654</v>
+        <v>0.6514065933376871</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524576742286832</v>
+        <v>0.652462398925532</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497220080886351</v>
+        <v>0.6497240229242983</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464211641756841</v>
+        <v>0.6464233285717811</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431300562899019</v>
+        <v>0.6431324382010798</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408125113941745</v>
+        <v>0.6408150318920128</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.639797119867671</v>
+        <v>0.639799642677609</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423435496570257</v>
+        <v>0.6423552744994094</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432385997527164</v>
+        <v>0.6432455831965288</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413317141419301</v>
+        <v>0.6413386552422213</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384544158359597</v>
+        <v>0.6384614472123038</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6402831926442984</v>
+        <v>0.6403038891040029</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403609438309747</v>
+        <v>0.6403809973582417</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398793192991449</v>
+        <v>0.6398897338406964</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422593358165314</v>
+        <v>0.6422676547943134</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.64498052613839</v>
+        <v>0.6449966655881383</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468594455245349</v>
+        <v>0.6468809086228857</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465112497489891</v>
+        <v>0.6465294666408361</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467543735033026</v>
+        <v>0.6467648526164006</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455168236672604</v>
+        <v>0.6455344215644132</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449420110388158</v>
+        <v>0.6449724542161255</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6456827065034205</v>
+        <v>0.6457350692239427</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434107500426616</v>
+        <v>0.6434792321290956</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425097763976053</v>
+        <v>0.6425969265051225</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6436168224200669</v>
+        <v>0.6437170494852322</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6441803974588127</v>
+        <v>0.6442865767532082</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6459230603836376</v>
+        <v>0.6460467420132276</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6526932252513933</v>
+        <v>0.6527966144014284</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6644769212134933</v>
+        <v>0.6646238351464778</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6717024927231348</v>
+        <v>0.6718669536273458</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.687645827005045</v>
+        <v>0.6877961522382554</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6968896229245249</v>
+        <v>0.6970029723237683</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6992394609060888</v>
+        <v>0.6993585078493698</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6995081580617568</v>
+        <v>0.6996300318245835</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.707917846404815</v>
+        <v>0.7079541659691521</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7079751025146949</v>
+        <v>0.7080036922596259</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109506046585545</v>
+        <v>0.7109347810862905</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7176718913533635</v>
+        <v>0.7175644411452198</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7178779687987487</v>
+        <v>0.7177633272783303</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7251276201388827</v>
+        <v>0.7249682508046948</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7201441644531257</v>
+        <v>0.7200766580722175</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7235414314751565</v>
+        <v>0.7234641736911572</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7230175799120436</v>
+        <v>0.7229510887866691</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7201305361930315</v>
+        <v>0.7200764148645913</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.714740958474668</v>
+        <v>0.7147401711083683</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166595398612348</v>
+        <v>0.7166498160554748</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166925350976431</v>
+        <v>0.716669603401095</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7154083647359196</v>
+        <v>0.7153833192591669</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131283277755209</v>
+        <v>0.7131120775377768</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7107044202345716</v>
+        <v>0.7106801410929087</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107357891963916</v>
+        <v>0.7107084972209539</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7086044931168695</v>
+        <v>0.708561737395618</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7061790945984051</v>
+        <v>0.7060964167472537</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7043543396704577</v>
+        <v>0.7048369841518972</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7034634418816627</v>
+        <v>0.7033906218012524</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028740267663236</v>
+        <v>0.702800222327552</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7032616034055246</v>
+        <v>0.7027949027133527</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7048508586445903</v>
+        <v>0.7042379342634175</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7062470619975035</v>
+        <v>0.705346552173477</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7083381106065416</v>
+        <v>0.7067316699361501</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7100471265903163</v>
+        <v>0.7087081771213283</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7099975029820361</v>
+        <v>0.7087120710699657</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.708881866306068</v>
+        <v>0.7078084398686532</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7068950306926172</v>
+        <v>0.7059187073301648</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7059857425923083</v>
+        <v>0.7042484403779661</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7066439034775758</v>
+        <v>0.7049570371829393</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7085343927947859</v>
+        <v>0.7076567896265202</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.7100253750379988</v>
+        <v>0.7093168766495218</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7106243569671464</v>
+        <v>0.711004250236738</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.7094075285981309</v>
+        <v>0.7103809597659253</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7071955045340976</v>
+        <v>0.7080285717374757</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7043848071472076</v>
+        <v>0.7053482031099583</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.6956248743097835</v>
+        <v>0.7013944774204441</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6861013551756628</v>
+        <v>0.6968943348789309</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6743501546457293</v>
+        <v>0.6883822142319099</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6627533723632648</v>
+        <v>0.6794583635090952</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6515452583699267</v>
+        <v>0.6710319491020829</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.6539734323474868</v>
+        <v>0.67329007765119</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>0.6608633942858556</v>
+        <v>0.6785521422917898</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -383,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" style="1" customWidth="1"/>
@@ -399,114 +399,962 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="3">
-        <v>46304</v>
+        <v>44743</v>
       </c>
       <c r="B2">
-        <v>0.697225</v>
+        <v>0.7020999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="3">
-        <v>46311</v>
+        <v>44778</v>
       </c>
       <c r="B3">
-        <v>0.6962603818363607</v>
+        <v>0.7025478862778352</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="3">
-        <v>46318</v>
+        <v>44806</v>
       </c>
       <c r="B4">
-        <v>0.6956035193671928</v>
+        <v>0.6952198047032108</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="3">
-        <v>46325</v>
+        <v>44834</v>
       </c>
       <c r="B5">
-        <v>0.6936835476988279</v>
+        <v>0.6783585634616704</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="3">
-        <v>46332</v>
+        <v>44869</v>
       </c>
       <c r="B6">
-        <v>0.6918618809822571</v>
+        <v>0.6765953734753085</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="3">
-        <v>46339</v>
+        <v>44897</v>
       </c>
       <c r="B7">
-        <v>0.6889474736620551</v>
+        <v>0.6759722954091933</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="3">
-        <v>46346</v>
+        <v>44932</v>
       </c>
       <c r="B8">
-        <v>0.6854739257404288</v>
+        <v>0.6733833143299141</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="3">
-        <v>46353</v>
+        <v>44960</v>
       </c>
       <c r="B9">
-        <v>0.6821141882361024</v>
+        <v>0.679397870419066</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="3">
-        <v>46360</v>
+        <v>44988</v>
       </c>
       <c r="B10">
-        <v>0.6789631107619948</v>
+        <v>0.6612690776309176</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="3">
-        <v>46367</v>
+        <v>45016</v>
       </c>
       <c r="B11">
-        <v>0.6740976364407272</v>
+        <v>0.6651977584628515</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="3">
-        <v>46374</v>
+        <v>45051</v>
       </c>
       <c r="B12">
-        <v>0.6692533937589663</v>
+        <v>0.6822630230906415</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="3">
-        <v>46381</v>
+        <v>45079</v>
       </c>
       <c r="B13">
-        <v>0.6629627063030868</v>
+        <v>0.6828070329577607</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="3">
-        <v>46388</v>
+        <v>45107</v>
       </c>
       <c r="B14">
-        <v>0.6563971681243943</v>
+        <v>0.6759462593448817</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="3">
+        <v>45142</v>
+      </c>
+      <c r="B15">
+        <v>0.6666511760041194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="3">
+        <v>45170</v>
+      </c>
+      <c r="B16">
+        <v>0.6532021885677427</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="3">
+        <v>45205</v>
+      </c>
+      <c r="B17">
+        <v>0.6450446754466707</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="3">
+        <v>45233</v>
+      </c>
+      <c r="B18">
+        <v>0.6450993108386855</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="3">
+        <v>45261</v>
+      </c>
+      <c r="B19">
+        <v>0.6451741346595923</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="3">
+        <v>45296</v>
+      </c>
+      <c r="B20">
+        <v>0.6512742564614972</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="3">
+        <v>45324</v>
+      </c>
+      <c r="B21">
+        <v>0.6570967680592356</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="3">
+        <v>45352</v>
+      </c>
+      <c r="B22">
+        <v>0.664085993049467</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="3">
+        <v>45387</v>
+      </c>
+      <c r="B23">
+        <v>0.6573122172572036</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="3">
+        <v>45415</v>
+      </c>
+      <c r="B24">
+        <v>0.6702237681713992</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="3">
+        <v>45443</v>
+      </c>
+      <c r="B25">
+        <v>0.6623290754486506</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="3">
+        <v>45478</v>
+      </c>
+      <c r="B26">
+        <v>0.6633720218132223</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="3">
+        <v>45506</v>
+      </c>
+      <c r="B27">
+        <v>0.659295400254539</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="3">
+        <v>45541</v>
+      </c>
+      <c r="B28">
+        <v>0.6530988452075037</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="3">
+        <v>45569</v>
+      </c>
+      <c r="B29">
+        <v>0.6717729033955471</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="3">
+        <v>45597</v>
+      </c>
+      <c r="B30">
+        <v>0.6651678681373596</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="3">
+        <v>45632</v>
+      </c>
+      <c r="B31">
+        <v>0.6500259637832642</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="3">
+        <v>45660</v>
+      </c>
+      <c r="B32">
+        <v>0.6233997941017151</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="3">
+        <v>45688</v>
+      </c>
+      <c r="B33">
+        <v>0.6197265703593156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="3">
+        <v>45716</v>
+      </c>
+      <c r="B34">
+        <v>0.6218480467796326</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="3">
+        <v>45751</v>
+      </c>
+      <c r="B35">
+        <v>0.6209017365758198</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="3">
+        <v>45779</v>
+      </c>
+      <c r="B36">
+        <v>0.6237200000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="3">
+        <v>45814</v>
+      </c>
+      <c r="B37">
+        <v>0.6463</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="3">
+        <v>45821</v>
+      </c>
+      <c r="B38">
+        <v>0.6437581543453469</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="3">
+        <v>45828</v>
+      </c>
+      <c r="B39">
+        <v>0.6432040853808826</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="3">
+        <v>45835</v>
+      </c>
+      <c r="B40">
+        <v>0.6420328265590491</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="3">
+        <v>45842</v>
+      </c>
+      <c r="B41">
+        <v>0.6419145400979437</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="3">
+        <v>45849</v>
+      </c>
+      <c r="B42">
+        <v>0.6505959580471182</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="3">
+        <v>45856</v>
+      </c>
+      <c r="B43">
+        <v>0.6514062944159147</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="3">
+        <v>45863</v>
+      </c>
+      <c r="B44">
+        <v>0.6524618893159676</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="3">
+        <v>45870</v>
+      </c>
+      <c r="B45">
+        <v>0.6497238060070384</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="3">
+        <v>45877</v>
+      </c>
+      <c r="B46">
+        <v>0.6464230954980446</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="3">
+        <v>45884</v>
+      </c>
+      <c r="B47">
+        <v>0.6431321816505078</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="3">
+        <v>45891</v>
+      </c>
+      <c r="B48">
+        <v>0.6408147603807716</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="3">
+        <v>45898</v>
+      </c>
+      <c r="B49">
+        <v>0.6397993708988536</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="3">
+        <v>45905</v>
+      </c>
+      <c r="B50">
+        <v>0.6423540090732363</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="3">
+        <v>45912</v>
+      </c>
+      <c r="B51">
+        <v>0.6432448291127074</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="3">
+        <v>45919</v>
+      </c>
+      <c r="B52">
+        <v>0.6413379057634438</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="3">
+        <v>45926</v>
+      </c>
+      <c r="B53">
+        <v>0.6384606880123218</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="3">
+        <v>45933</v>
+      </c>
+      <c r="B54">
+        <v>0.6403016547607244</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="3">
+        <v>45940</v>
+      </c>
+      <c r="B55">
+        <v>0.6403788333858853</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="3">
+        <v>45947</v>
+      </c>
+      <c r="B56">
+        <v>0.6398886106333241</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="3">
+        <v>45954</v>
+      </c>
+      <c r="B57">
+        <v>0.6422667560349113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="3">
+        <v>45961</v>
+      </c>
+      <c r="B58">
+        <v>0.6449949230527698</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="3">
+        <v>45968</v>
+      </c>
+      <c r="B59">
+        <v>0.6468785935018484</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="3">
+        <v>45975</v>
+      </c>
+      <c r="B60">
+        <v>0.6465275024877959</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="3">
+        <v>45982</v>
+      </c>
+      <c r="B61">
+        <v>0.6467637224537756</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="3">
+        <v>45989</v>
+      </c>
+      <c r="B62">
+        <v>0.6455325232370936</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="3">
+        <v>45996</v>
+      </c>
+      <c r="B63">
+        <v>0.6449691687495223</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="3">
+        <v>46003</v>
+      </c>
+      <c r="B64">
+        <v>0.6457294209032323</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="3">
+        <v>46010</v>
+      </c>
+      <c r="B65">
+        <v>0.6434718457867006</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="3">
+        <v>46017</v>
+      </c>
+      <c r="B66">
+        <v>0.6425875265878411</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="3">
+        <v>46024</v>
+      </c>
+      <c r="B67">
+        <v>0.6437062409757851</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="3">
+        <v>46031</v>
+      </c>
+      <c r="B68">
+        <v>0.6442751283199529</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="3">
+        <v>46038</v>
+      </c>
+      <c r="B69">
+        <v>0.6460334055120414</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="3">
+        <v>46045</v>
+      </c>
+      <c r="B70">
+        <v>0.6527854585489661</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="3">
+        <v>46052</v>
+      </c>
+      <c r="B71">
+        <v>0.6646079882431276</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="3">
+        <v>46059</v>
+      </c>
+      <c r="B72">
+        <v>0.6718492130544327</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="3">
+        <v>46066</v>
+      </c>
+      <c r="B73">
+        <v>0.6877799533598872</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="3">
+        <v>46073</v>
+      </c>
+      <c r="B74">
+        <v>0.6969907602724287</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="3">
+        <v>46080</v>
+      </c>
+      <c r="B75">
+        <v>0.6993456873392159</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="3">
+        <v>46087</v>
+      </c>
+      <c r="B76">
+        <v>0.6996169159071171</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="3">
+        <v>46094</v>
+      </c>
+      <c r="B77">
+        <v>0.7079502724278092</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="3">
+        <v>46101</v>
+      </c>
+      <c r="B78">
+        <v>0.7080006353252685</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="3">
+        <v>46108</v>
+      </c>
+      <c r="B79">
+        <v>0.7109365144526305</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="3">
+        <v>46115</v>
+      </c>
+      <c r="B80">
+        <v>0.7175760329830779</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="3">
+        <v>46122</v>
+      </c>
+      <c r="B81">
+        <v>0.7177756885399948</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="3">
+        <v>46129</v>
+      </c>
+      <c r="B82">
+        <v>0.7249854204437395</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="3">
+        <v>46136</v>
+      </c>
+      <c r="B83">
+        <v>0.7200839332120619</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="3">
+        <v>46143</v>
+      </c>
+      <c r="B84">
+        <v>0.7234724973846745</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="3">
+        <v>46150</v>
+      </c>
+      <c r="B85">
+        <v>0.7229582452239509</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" s="3">
+        <v>46157</v>
+      </c>
+      <c r="B86">
+        <v>0.7200822342618671</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="3">
+        <v>46164</v>
+      </c>
+      <c r="B87">
+        <v>0.7147402536595063</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" s="3">
+        <v>46171</v>
+      </c>
+      <c r="B88">
+        <v>0.7166508570974626</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="3">
+        <v>46178</v>
+      </c>
+      <c r="B89">
+        <v>0.7166720709165593</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" s="3">
+        <v>46185</v>
+      </c>
+      <c r="B90">
+        <v>0.7153860184335882</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="3">
+        <v>46192</v>
+      </c>
+      <c r="B91">
+        <v>0.7131138363896385</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" s="3">
+        <v>46199</v>
+      </c>
+      <c r="B92">
+        <v>0.7106827753379817</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="3">
+        <v>46206</v>
+      </c>
+      <c r="B93">
+        <v>0.7107114579297953</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" s="3">
+        <v>46213</v>
+      </c>
+      <c r="B94">
+        <v>0.7085663687817751</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B95">
+        <v>0.7061053316497197</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B96">
+        <v>0.7048471661008523</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B97">
+        <v>0.7034001873410736</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" s="3">
+        <v>46241</v>
+      </c>
+      <c r="B98">
+        <v>0.7028074722386274</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="3">
+        <v>46248</v>
+      </c>
+      <c r="B99">
+        <v>0.7027984329912027</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B100">
+        <v>0.7042355927871236</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B101">
+        <v>0.7053342118484991</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" s="3">
+        <v>46269</v>
+      </c>
+      <c r="B102">
+        <v>0.7067118745699439</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="3">
+        <v>46276</v>
+      </c>
+      <c r="B103">
+        <v>0.7086837465202871</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="3">
+        <v>46283</v>
+      </c>
+      <c r="B104">
+        <v>0.7086833318063277</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="3">
+        <v>46290</v>
+      </c>
+      <c r="B105">
+        <v>0.7077835661662575</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="3">
+        <v>46297</v>
+      </c>
+      <c r="B106">
+        <v>0.7059013279185029</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="3">
+        <v>46304</v>
+      </c>
+      <c r="B107">
+        <v>0.7042405356763835</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="3">
+        <v>46311</v>
+      </c>
+      <c r="B108">
+        <v>0.7046089620148683</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="3">
+        <v>46318</v>
+      </c>
+      <c r="B109">
+        <v>0.7071737113422627</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" s="3">
+        <v>46325</v>
+      </c>
+      <c r="B110">
+        <v>0.708790601353618</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="3">
+        <v>46332</v>
+      </c>
+      <c r="B111">
+        <v>0.7103413851730074</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" s="3">
+        <v>46339</v>
+      </c>
+      <c r="B112">
+        <v>0.709584472125911</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="3">
+        <v>46346</v>
+      </c>
+      <c r="B113">
+        <v>0.7071443752289965</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="3">
+        <v>46353</v>
+      </c>
+      <c r="B114">
+        <v>0.7043813419417947</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="3">
+        <v>46360</v>
+      </c>
+      <c r="B115">
+        <v>0.700396485423445</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="3">
+        <v>46367</v>
+      </c>
+      <c r="B116">
+        <v>0.6958929968444563</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="3">
+        <v>46374</v>
+      </c>
+      <c r="B117">
+        <v>0.6874677827330589</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" s="3">
+        <v>46381</v>
+      </c>
+      <c r="B118">
+        <v>0.6786525481650565</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="3">
+        <v>46388</v>
+      </c>
+      <c r="B119">
+        <v>0.6703216379087852</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="3">
         <v>46395</v>
       </c>
-      <c r="B15">
-        <v>0.6507713291002191</v>
+      <c r="B120">
+        <v>0.6713921259701786</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="3">
+        <v>46402</v>
+      </c>
+      <c r="B121">
+        <v>0.6712985834749675</v>
       </c>
     </row>
   </sheetData>

--- a/public/data/files/AUDUSD_forecast.xlsx
+++ b/public/data/files/AUDUSD_forecast.xlsx
@@ -722,7 +722,7 @@
         <v>45849</v>
       </c>
       <c r="B42">
-        <v>0.6505959580471182</v>
+        <v>0.6505954037192365</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -730,7 +730,7 @@
         <v>45856</v>
       </c>
       <c r="B43">
-        <v>0.6514062944159147</v>
+        <v>0.6514060006368573</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -738,7 +738,7 @@
         <v>45863</v>
       </c>
       <c r="B44">
-        <v>0.6524618893159676</v>
+        <v>0.6524613885313693</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -746,7 +746,7 @@
         <v>45870</v>
       </c>
       <c r="B45">
-        <v>0.6497238060070384</v>
+        <v>0.6497235927508124</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -754,7 +754,7 @@
         <v>45877</v>
       </c>
       <c r="B46">
-        <v>0.6464230954980446</v>
+        <v>0.6464228663709609</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -762,7 +762,7 @@
         <v>45884</v>
       </c>
       <c r="B47">
-        <v>0.6431321816505078</v>
+        <v>0.6431319294567875</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -770,7 +770,7 @@
         <v>45891</v>
       </c>
       <c r="B48">
-        <v>0.6408147603807716</v>
+        <v>0.6408144934884252</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -778,7 +778,7 @@
         <v>45898</v>
       </c>
       <c r="B49">
-        <v>0.6397993708988536</v>
+        <v>0.6397991037478958</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -786,7 +786,7 @@
         <v>45905</v>
       </c>
       <c r="B50">
-        <v>0.6423540090732363</v>
+        <v>0.642352765743227</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -794,7 +794,7 @@
         <v>45912</v>
       </c>
       <c r="B51">
-        <v>0.6432448291127074</v>
+        <v>0.6432440882863067</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -802,7 +802,7 @@
         <v>45919</v>
       </c>
       <c r="B52">
-        <v>0.6413379057634438</v>
+        <v>0.6413371694534222</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -810,7 +810,7 @@
         <v>45926</v>
       </c>
       <c r="B53">
-        <v>0.6384606880123218</v>
+        <v>0.6384599421456567</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -818,7 +818,7 @@
         <v>45933</v>
       </c>
       <c r="B54">
-        <v>0.6403016547607244</v>
+        <v>0.6402994595824206</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -826,7 +826,7 @@
         <v>45940</v>
       </c>
       <c r="B55">
-        <v>0.6403788333858853</v>
+        <v>0.6403767071182614</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -834,7 +834,7 @@
         <v>45947</v>
       </c>
       <c r="B56">
-        <v>0.6398886106333241</v>
+        <v>0.6398875068497952</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -842,7 +842,7 @@
         <v>45954</v>
       </c>
       <c r="B57">
-        <v>0.6422667560349113</v>
+        <v>0.6422658731852868</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -850,7 +850,7 @@
         <v>45961</v>
       </c>
       <c r="B58">
-        <v>0.6449949230527698</v>
+        <v>0.644993211098225</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -858,7 +858,7 @@
         <v>45968</v>
       </c>
       <c r="B59">
-        <v>0.6468785935018484</v>
+        <v>0.6468763184929374</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -866,7 +866,7 @@
         <v>45975</v>
       </c>
       <c r="B60">
-        <v>0.6465275024877959</v>
+        <v>0.6465255721740922</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -874,7 +874,7 @@
         <v>45982</v>
       </c>
       <c r="B61">
-        <v>0.6467637224537756</v>
+        <v>0.646762611832803</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -882,7 +882,7 @@
         <v>45989</v>
       </c>
       <c r="B62">
-        <v>0.6455325232370936</v>
+        <v>0.6455306578304671</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -890,7 +890,7 @@
         <v>45996</v>
       </c>
       <c r="B63">
-        <v>0.6449691687495223</v>
+        <v>0.6449659406100261</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -898,7 +898,7 @@
         <v>46003</v>
       </c>
       <c r="B64">
-        <v>0.6457294209032323</v>
+        <v>0.645723870495817</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -906,7 +906,7 @@
         <v>46010</v>
       </c>
       <c r="B65">
-        <v>0.6434718457867006</v>
+        <v>0.6434645873054844</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -914,7 +914,7 @@
         <v>46017</v>
       </c>
       <c r="B66">
-        <v>0.6425875265878411</v>
+        <v>0.6425782894050215</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -922,7 +922,7 @@
         <v>46024</v>
       </c>
       <c r="B67">
-        <v>0.6437062409757851</v>
+        <v>0.6436956191433277</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -930,7 +930,7 @@
         <v>46031</v>
       </c>
       <c r="B68">
-        <v>0.6442751283199529</v>
+        <v>0.6442638771508148</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -938,7 +938,7 @@
         <v>46038</v>
       </c>
       <c r="B69">
-        <v>0.6460334055120414</v>
+        <v>0.6460202990261329</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -946,7 +946,7 @@
         <v>46045</v>
       </c>
       <c r="B70">
-        <v>0.6527854585489661</v>
+        <v>0.6527744968662099</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -954,7 +954,7 @@
         <v>46052</v>
       </c>
       <c r="B71">
-        <v>0.6646079882431276</v>
+        <v>0.6645924158970395</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -962,7 +962,7 @@
         <v>46059</v>
       </c>
       <c r="B72">
-        <v>0.6718492130544327</v>
+        <v>0.6718317800739497</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -970,7 +970,7 @@
         <v>46066</v>
       </c>
       <c r="B73">
-        <v>0.6877799533598872</v>
+        <v>0.6877640313715833</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -978,7 +978,7 @@
         <v>46073</v>
       </c>
       <c r="B74">
-        <v>0.6969907602724287</v>
+        <v>0.696978756407194</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -986,7 +986,7 @@
         <v>46080</v>
       </c>
       <c r="B75">
-        <v>0.6993456873392159</v>
+        <v>0.6993330841161866</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -994,7 +994,7 @@
         <v>46087</v>
       </c>
       <c r="B76">
-        <v>0.6996169159071171</v>
+        <v>0.6996040201523084</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1002,7 +1002,7 @@
         <v>46094</v>
       </c>
       <c r="B77">
-        <v>0.7079502724278092</v>
+        <v>0.7079464406741418</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1010,7 +1010,7 @@
         <v>46101</v>
       </c>
       <c r="B78">
-        <v>0.7080006353252685</v>
+        <v>0.7079976250192813</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1018,7 +1018,7 @@
         <v>46108</v>
       </c>
       <c r="B79">
-        <v>0.7109365144526305</v>
+        <v>0.7109382115376626</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1026,7 +1026,7 @@
         <v>46115</v>
       </c>
       <c r="B80">
-        <v>0.7175760329830779</v>
+        <v>0.7175874235856615</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1034,7 +1034,7 @@
         <v>46122</v>
       </c>
       <c r="B81">
-        <v>0.7177756885399948</v>
+        <v>0.7177878367163437</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1042,7 +1042,7 @@
         <v>46129</v>
       </c>
       <c r="B82">
-        <v>0.7249854204437395</v>
+        <v>0.7250022974954162</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1050,7 +1050,7 @@
         <v>46136</v>
       </c>
       <c r="B83">
-        <v>0.7200839332120619</v>
+        <v>0.7200910838268348</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1058,7 +1058,7 @@
         <v>46143</v>
       </c>
       <c r="B84">
-        <v>0.7234724973846745</v>
+        <v>0.7234806791619435</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1066,7 +1066,7 @@
         <v>46150</v>
       </c>
       <c r="B85">
-        <v>0.7229582452239509</v>
+        <v>0.7229652813592485</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1074,7 +1074,7 @@
         <v>46157</v>
       </c>
       <c r="B86">
-        <v>0.7200822342618671</v>
+        <v>0.7200879571710437</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1082,7 +1082,7 @@
         <v>46164</v>
       </c>
       <c r="B87">
-        <v>0.7147402536595063</v>
+        <v>0.714740335340506</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1090,7 +1090,7 @@
         <v>46171</v>
       </c>
       <c r="B88">
-        <v>0.7166508570974626</v>
+        <v>0.7166518819426664</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1098,7 +1098,7 @@
         <v>46178</v>
       </c>
       <c r="B89">
-        <v>0.7166720709165593</v>
+        <v>0.7166744970951131</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1106,7 +1106,7 @@
         <v>46185</v>
       </c>
       <c r="B90">
-        <v>0.7153860184335882</v>
+        <v>0.7153886713946549</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1114,7 +1114,7 @@
         <v>46192</v>
       </c>
       <c r="B91">
-        <v>0.7131138363896385</v>
+        <v>0.7131155633467636</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1122,7 +1122,7 @@
         <v>46199</v>
       </c>
       <c r="B92">
-        <v>0.7106827753379817</v>
+        <v>0.7106853603202846</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1130,7 +1130,7 @@
         <v>46206</v>
       </c>
       <c r="B93">
-        <v>0.7107114579297953</v>
+        <v>0.71071436337079</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1138,7 +1138,7 @@
         <v>46213</v>
       </c>
       <c r="B94">
-        <v>0.7085663687817751</v>
+        <v>0.7085709153308553</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1146,7 +1146,7 @@
         <v>46220</v>
       </c>
       <c r="B95">
-        <v>0.7061053316497197</v>
+        <v>0.7061140928664759</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1154,7 +1154,7 @@
         <v>46227</v>
       </c>
       <c r="B96">
-        <v>0.7048471661008523</v>
+        <v>0.7048571769864165</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1162,7 +1162,7 @@
         <v>46234</v>
       </c>
       <c r="B97">
-        <v>0.7034001873410736</v>
+        <v>0.703409598311506</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1170,7 +1170,7 @@
         <v>46241</v>
       </c>
       <c r="B98">
-        <v>0.7028074722386274</v>
+        <v>0.7028146144344902</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1178,7 +1178,7 @@
         <v>46248</v>
       </c>
       <c r="B99">
-        <v>0.7027984329912027</v>
+        <v>0.7028019238936083</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1186,7 +1186,7 @@
         <v>46255</v>
       </c>
       <c r="B100">
-        <v>0.7042355927871236</v>
+        <v>0.7042333165060612</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1194,7 +1194,7 @@
         <v>46262</v>
       </c>
       <c r="B101">
-        <v>0.7053342118484991</v>
+        <v>0.705322101583097</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1202,7 +1202,7 @@
         <v>46269</v>
       </c>
       <c r="B102">
-        <v>0.7067118745699439</v>
+        <v>0.7066924240964236</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1210,7 +1210,7 @@
         <v>46276</v>
       </c>
       <c r="B103">
-        <v>0.7086837465202871</v>
+        <v>0.708659727636861</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1218,7 +1218,7 @@
         <v>46283</v>
       </c>
       <c r="B104">
-        <v>0.7086833318063277</v>
+        <v>0.708655042576026</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1226,7 +1226,7 @@
         <v>46290</v>
       </c>
       <c r="B105">
-        <v>0.7077835661662575</v>
+        <v>0.7077590402407179</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1234,7 +1234,7 @@
         <v>46297</v>
       </c>
       <c r="B106">
-        <v>0.7059013279185029</v>
+        <v>0.7058841398919731</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1242,7 +1242,7 @@
         <v>46304</v>
       </c>
       <c r="B107">
-        <v>0.7042405356763835</v>
+        <v>0.7042326584536185</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1250,7 +1250,7 @@
         <v>46311</v>
       </c>
       <c r="B108">
-        <v>0.7046089620148683</v>
+        <v>0.7043937546569423</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1258,7 +1258,7 @@
         <v>46318</v>
       </c>
       <c r="B109">
-        <v>0.7071737113422627</v>
+        <v>0.706861193089354</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1266,7 +1266,7 @@
         <v>46325</v>
       </c>
       <c r="B110">
-        <v>0.708790601353618</v>
+        <v>0.7084594771923034</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1274,7 +1274,7 @@
         <v>46332</v>
       </c>
       <c r="B111">
-        <v>0.7103413851730074</v>
+        <v>0.7099370173321498</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1282,7 +1282,7 @@
         <v>46339</v>
       </c>
       <c r="B112">
-        <v>0.709584472125911</v>
+        <v>0.7090817868565513</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1290,7 +1290,7 @@
         <v>46346</v>
       </c>
       <c r="B113">
-        <v>0.7071443752289965</v>
+        <v>0.7065851292442691</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1298,7 +1298,7 @@
         <v>46353</v>
       </c>
       <c r="B114">
-        <v>0.7043813419417947</v>
+        <v>0.7037865392462346</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1306,7 +1306,7 @@
         <v>46360</v>
       </c>
       <c r="B115">
-        <v>0.700396485423445</v>
+        <v>0.6998311008951661</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1314,7 +1314,7 @@
         <v>46367</v>
       </c>
       <c r="B116">
-        <v>0.6958929968444563</v>
+        <v>0.6954050552696178</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1322,7 +1322,7 @@
         <v>46374</v>
       </c>
       <c r="B117">
-        <v>0.6874677827330589</v>
+        <v>0.6871987331196949</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1330,7 +1330,7 @@
         <v>46381</v>
       </c>
       <c r="B118">
-        <v>0.6786525481650565</v>
+        <v>0.6786568373927937</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1338,7 +1338,7 @@
         <v>46388</v>
       </c>
       <c r="B119">
-        <v>0.6703216379087852</v>
+        <v>0.6707019896913876</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1346,7 +1346,7 @@
         <v>46395</v>
       </c>
       <c r="B120">
-        <v>0.6713921259701786</v>
+        <v>0.6714606598424109</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1354,7 +1354,7 @@
         <v>46402</v>
       </c>
       <c r="B121">
-        <v>0.6712985834749675</v>
+        <v>0.671165828943261</v>
       </c>
     </row>
   </sheetData>
